--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -113,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
@@ -145,6 +145,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -702,6 +705,13 @@
       <c r="A19" t="inlineStr">
         <is>
           <t>v9: القوالب: أُعيدت صياغة 12 قالباً وأُضيف 10 (البداية، الخصوصية، بعد «لا» و«نعم»، الإدخال غير المفهوم، ما بقي غير مغطى، الآيات). كلها «مسودة» حتى تعتمدها.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v10: أُضيفت 4 مقاطع من الموسوعة العقدية (الدرر): ق-01 تعريف القرآن، ق-33 مراحل الجمع، ق-34 التعريف اللغوي، ق-35 الفرق بين القرآن والحديث القدسي. الحالة «جاهز للمراجعة».</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:V33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2107,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="160" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
           <t>ق-01</t>
@@ -2130,36 +2140,65 @@
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>الدرر 1363 / 1365</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr"/>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="5" t="inlineStr"/>
-      <c r="J2" s="6" t="inlineStr"/>
+          <t>المبحث الثاني: تعريف القرآن اصطلاحاً، الفقرة الأولى — https://dorar.net/aqeeda/1365</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>القُرْآنُ الكريمُ هو اسمٌ لكلامِ اللهِ تعالى وكِتابِه، المنَزَّلُ على عَبدِه ورَسولِه مُحَمَّدٍ صلَّى اللهُ عليه وسلَّم بواسِطةِ جِبريلَ عليه السَّلامُ بلِسانٍ عَربيٍّ مُبِينٍ، المنقولُ إلينا بالتواتُرِ، المكتوبُ في المُصحَفِ، المتعَبَّدُ بتلاوتِه، المبدوءُ بسُورةِ الفاتحةِ، والمختومُ بسُورةِ النَّاسِ، والمُعجِزُ بأقصَرِ سُوَرِه .</t>
+        </is>
+      </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>تعريف القرآن</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
-      <c r="N2" s="6" t="inlineStr"/>
-      <c r="O2" s="6" t="inlineStr"/>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="6" t="inlineStr"/>
-      <c r="R2" s="6" t="inlineStr"/>
+          <t>ما القرآن؟ تعريفه: كلام الله المنزل على محمد ﷺ بواسطة جبريل، بلسان عربي، المنقول بالتواتر، المكتوب في المصحف، المتعبد بتلاوته.</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>ما هو القرآن؟ | ما تعريف القرآن؟ | إيش يعني القرآن؟ | من أين جاء القرآن؟</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="n"/>
+      <c r="Q2" s="6" t="n"/>
+      <c r="R2" s="6" t="n"/>
       <c r="S2" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T2" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T2" s="6" t="inlineStr">
+        <is>
+          <t>فقرة كاملة من رأس المبحث.</t>
+        </is>
+      </c>
       <c r="U2" s="9">
         <f>IF(A2="","",IF(J2="","لم يُستخرج بعد",IF(OR(M2="ج",M2="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D2,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D2,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B2="",E2="",K2="",M2="",N2=""),"بيانات ناقصة",IF(P2&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q2="","المراجعة غير موثقة",IF(AND(N2="نعم",R2="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N2="نعم",R2&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S2&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
       </c>
+      <c r="V2" s="12" t="n"/>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
@@ -3109,7 +3148,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
+    <row r="16" ht="160" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ق-33</t>
@@ -3132,36 +3171,70 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>الدرر 1413</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="6" t="inlineStr"/>
+          <t>المطلب الثاني: حفظ القرآن في عهد الصحابة، كلام ابن عثيمين في مراحل الجمع (مع قصّ) — https://dorar.net/aqeeda/1413</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>وقال ابنُ عُثَيمين: (لكِتابةِ القُرْآنِ وجمعِه ثلاثُ مَراحِلَ:
+المَرحلةُ الأُولى: في عَهدِ النَّبيِّ صلَّى اللهُ عليه وسلَّم، وكان الاعتمادُ في هذه المرحلةِ على الحِفظِ أكثَرَ من الاعتمادِ على الكِتابةِ؛ لقُوَّةِ الذَّاكِرةِ وسُرعةِ الِحفظِ، وقِلَّةِ الكاتِبينَ ووسائِلِ الكِتابةِ؛ ولذلك لم يُجمَعْ في مُصحَفٍ، بل كان من سمع آيةً حَفِظها، أو كتبها فيما تيسَّر له من عُسُبِ النَّخلِ، ورِقاعِ الجُلودِ، ولخافِ الحِجارةِ، وكِسَرِ الأكتافِ، وكان القُرَّاءُ عددًا كبيرًا.
+[…]
+المَرحَلةُ الثَّانيةُ: في عَهدِ أبي بكرٍ رَضِيَ اللهُ عنه في السَّنةِ الثَّانيةَ عَشرةَ من الهِجرةِ. وسَبَبُه أنَّه قُتِل في وقعةِ اليمامةِ عَدَدٌ كبيرٌ مِن القُرَّاءِ؛ منهم سالمٌ مولى أبي حُذَيفةَ؛ أحدُ من أمر النَّبيُّ صلَّى اللهُ عليه وسلَّم بأخْذِ القُرْآنِ منهم .
+فأمر أبو بكرٍ رَضِيَ اللهُ عنه بجَمْعِه؛ لئلَّا يضيعَ... وقد وافق المُسلِمون أبا بكرٍ على ذلك وعدُّوه من حسَناتِه، حتى قال عليٌّ رَضِيَ اللهُ عنه: أعظَمُ النَّاسِ في المصاحِفِ أجرًا أبو بكرٍ، رحمةُ اللهِ على أبي بكرٍ؛ هو أوَّلُ من جمع كِتابَ اللهِ.
+المَرحَلةُ الثَّالِثُةُ: في عَهدِ أميرِ المُؤمِنين عثمانَ بنِ عَفَّانَ رَضِيَ اللهُ عنه في السَّنةِ الخامِسةِ والعِشرينَ. وسَبَبُه اختلافُ النَّاسِ في القراءةِ بحسَبِ اختلافِ الصُّحُفِ التي في أيدي الصَّحابةِ رَضِيَ اللهُ عنهم، فخِيفَت الفِتنةُ، فأمَرَ عُثمانُ رَضِيَ اللهُ عنه أن تُجمَعَ هذه الصُّحُفُ في مُصحَفٍ واحدٍ؛ لئلَّا يختَلِفَ النَّاسُ، فيتنازعوا في كِتابِ اللهِ تعالى ويتفَرَّقوا... وقد فعل عثمانُ رَضِيَ اللهُ عنه هذا بعد أن استشار الصَّحابةَ رَضِيَ اللهُ عنهم […] وقد بقي على ما كان عليه حتى الآن متَّفَقًا عليه بين المُسلِمين متواتِرًا بينهم، يتلقَّاه الصغيرُ عن الكبيرِ، لم تعبَثْ به أيدي المفسِدين، ولم تطمِسْه أهواءُ الزَّائغِين. فللَّهِ الحمدُ رَبِّ السَّمَواتِ ورَبِّ الأرضِ رَبِّ العالَمين) .</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>حفظ القرآن في عهد الصحابة</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
-      <c r="N16" s="6" t="inlineStr"/>
-      <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="6" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr"/>
+          <t>مراحل جمع القرآن الثلاث: في عهد النبي ﷺ حفظاً وكتابة متفرقة، ثم في عهد أبي بكر، ثم في عهد عثمان رضي الله عنهما، وبقاؤه متواتراً إلى اليوم.</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>كيف جُمع القرآن؟ | متى صار القرآن كتاباً واحداً؟ | لماذا جمع أبو بكر القرآن؟ | لماذا جمع عثمان القرآن؟ | هل تغيّر القرآن منذ زمن الصحابة؟</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>قول علي رضي الله عنه في فضل أبي بكر (أثر منقول في كلام ابن عثيمين)</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="6" t="n"/>
+      <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T16" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>قصّتان معلّمتان «[…]»: حذفت حديث القرّاء السبعين (بئر معونة)، وحذفت أثرَي ابن أبي داود ومصعب بن سعد في تحريق المصاحف التزاماً بحدود ح3. علامات «...» من المصدر نفسه.</t>
+        </is>
+      </c>
       <c r="U16" s="9">
         <f>IF(A16="","",IF(J16="","لم يُستخرج بعد",IF(OR(M16="ج",M16="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D16,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D16,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B16="",E16="",K16="",M16="",N16=""),"بيانات ناقصة",IF(P16&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q16="","المراجعة غير موثقة",IF(AND(N16="نعم",R16="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N16="نعم",R16&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S16&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
       </c>
+      <c r="V16" s="12" t="n"/>
     </row>
     <row r="17" ht="120" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -4525,8 +4598,177 @@
         </is>
       </c>
     </row>
+    <row r="32" ht="160" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>ق-34</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>إضافي</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>المبحث الأول: تعريف القرآن لغةً — https://dorar.net/aqeeda/1363</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>القُرآنُ في الأصلِ مَصدَرٌ، يقالُ: قَرَأَ يَقْرَأُ قِراءةً وقُرْآنًا، ثمَّ أُطلِقَ على المقروءِ، وسُمِّي القُرآنُ قُرآنًا؛ لأنَّه يجمَعُ السُّوَرَ فيَضُمُّها، وكُلُّ شَيءٍ جَمَعْتَه فقد قرَأْتَه، وأصلُ (قرأ): يَدُلُّ على جَمعٍ واجْتِماعٍ</t>
+        </is>
+      </c>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>معنى كلمة «قرآن» في اللغة، ولماذا سُمّي القرآن بهذا الاسم.</t>
+        </is>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>ما معنى كلمة قرآن؟ | لماذا سمي القرآن قرآناً؟</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="n"/>
+      <c r="Q32" s="6" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>المبحث كاملاً.</t>
+        </is>
+      </c>
+      <c r="U32" s="9">
+        <f>IF(A32="","",IF(J32="","لم يُستخرج بعد",IF(OR(M32="ج",M32="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D32,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D32,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B32="",E32="",K32="",M32="",N32=""),"بيانات ناقصة",IF(P32&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q32="","المراجعة غير موثقة",IF(AND(N32="نعم",R32="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N32="نعم",R32&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S32&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+      <c r="V32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="160" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ق-35</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>إضافي</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>المبحث الثاني: الفرق بين القرآن الكريم والحديث القدسي، الفروق 1–4 من 13 — https://dorar.net/aqeeda/1365</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>1- أنَّ القُرْآنَ الكريمَ تحدَّى اللهُ النَّاسَ أن يأتُوا بمِثْلِه، أو بعَشْرِ سُوَرٍ مِثْلِه، أو بسُورةٍ مِن مِثْلِه، أو بحديثٍ مِثْلِه؛ فعَجَزوا. أمَّا الحديثُ القُدُسيُّ فلم يقَعْ به التحَدِّي والإعجازُ.
+2- أنَّ القُرْآنَ الكريمَ منقولٌ بطريقِ التواتُرِ، فهو قَطعيُّ الثُّبوتِ كُلُّه؛ سُوَرُه وآياتُه، وجُمَلُه ومُفرداتُه، وحُروفُه وحَرَكاتُه وسَكَناتُه، أمَّا الحديثُ القُدُسيُّ فأغلَبُه أحاديثُ آحادٍ ظَنِّيُّ الثُّبوتِ.
+3- أنَّ القُرْآنَ الكريمَ مِن عِندِ اللهِ لفظًا ومعنًى، أمَّا الحديثُ القُدُسيُّ فمعناه من اللهِ باتِّفاقِ العُلَماءِ، أمَّا لَفظُه فاختُلِف فيه.
+4- أنَّ القُرْآنَ الكريمَ لا يُنسَبُ إلَّا إلى اللهِ تعالى، أمَّا الحديثُ القُدُسيُّ فيُنسَبُ إلى اللهِ تعالى نسبةَ إنشاءٍ، فيُقالُ: قال اللهُ تعالى، ويُروى مضافًا إلى الرَّسولِ الله صلَّى اللهُ عليه وسلَّم نِسبةَ إخبارٍ، فيُقالُ: قال رَسولُ اللهِ صلَّى اللهُ عليه وسلَّم فيما يرويه عن رَبِّه.</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>الفرق بين القرآن الكريم والحديث القدسي: التحدي بالقرآن، وتواتره، وأنه من الله لفظاً ومعنى، ونسبته إلى الله.</t>
+        </is>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>ما الفرق بين القرآن والحديث القدسي؟ | هل الحديث القدسي من القرآن؟ | ما الفرق بين القرآن والحديث؟</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>اخترت الفروق 1–4 من 13؛ تركت 5 و6 و10 و11 لأنها أحكام فقهية (الجنب، الصلاة، التكفير، الاستعاذة)، وتركت 7–9 و12–13 للطول.</t>
+        </is>
+      </c>
+      <c r="U33" s="9">
+        <f>IF(A33="","",IF(J33="","لم يُستخرج بعد",IF(OR(M33="ج",M33="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D33,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D33,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B33="",E33="",K33="",M33="",N33=""),"بيانات ناقصة",IF(P33&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q33="","المراجعة غير موثقة",IF(AND(N33="نعم",R33="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N33="نعم",R33&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S33&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+      <c r="V33" s="12" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V31"/>
+  <autoFilter ref="A1:V33"/>
   <conditionalFormatting sqref="N2:N60">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N2="نعم"</formula>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -712,6 +712,13 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>v10: أُضيفت 4 مقاطع من الموسوعة العقدية (الدرر): ق-01 تعريف القرآن، ق-33 مراحل الجمع، ق-34 التعريف اللغوي، ق-35 الفرق بين القرآن والحديث القدسي. الحالة «جاهز للمراجعة».</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v11: أُضيفت 5 مقاطع من الدرر: ق-02 مكانة القرآن، ق-03 هيمنته على الكتب السابقة (حساس)، ق-09 نزوله في رمضان، ق-36 فضل تلاوته، ق-37 نزوله منجّماً. ق-18 صار إضافياً.</t>
         </is>
       </c>
     </row>
@@ -726,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1297,12 +1304,53 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="220" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>ق-03</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>الموسوعة العقدية — هيمنة القرآن على الكتب السابقة</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>قال اللهُ تعالى: ﴿وَأَنْزَلْنَا إِلَيْكَ الْكِتَابَ بِالْحَقِّ مُصَدِّقًا لِمَا بَيْنَ يَدَيْهِ مِنَ الْكِتَابِ وَمُهَيْمِنًا عَلَيْهِ فَاحْكُمْ بَيْنَهم بِمَا أَنْزَلَ اللَّهُ﴾ [المائدة: 48] .
+أي: وأنزلْناه شاهدًا للكتُبِ الإلهيَّةِ السَّابقةِ بصِدقها، وموافقًا لها، ومطابِقًا لأخبارِها وأصولِ شرائِعِها، وفي وجودِه أيضًا دَلالةٌ على صِدقِها؛ لأنَّها أَخبرتْ بنُزولِ القُرآنِ. وأنزلْناه أمينًا على الكتُبِ الإلهيَّةِ السَّابقةِ، حافظًا لها، مُشتَمِلًا على ما اشتملَتْ عليه الكتُبُ السَّابقَةُ وزيادةٍ، وناسِخًا لها، وحاكمًا عليها كلِّها، فما شهِد له القُرْآنُ منها بالصِّدقِ فهو مقبولٌ، وما شهِد له بالردِّ فهو مردودٌ، قد دخلَه التحريفُ والتبديلُ، وإلَّا فلو كان مِن عِندِ اللهِ تعالى لم يُخالِفْه. وما دام أنَّ هذه هي حالُ القُرْآنِ؛ فاحكُمْ إذنْ -يا محمَّدُ- بينَ أهلِ الكِتاب وغيرِهم بهذا القُرْآنِ العظيمِ في كلِّ ما احتَكموا فيه إليك .
+[…]
+وقال ابنُ كثيرٍ: (جعل اللهُ هذا الكِتابَ العظيمَ الذي أنزله آخِرَ الكُتُبِ وخاتِمَها وأشمَلَها وأعظَمَها وأكمَلَها؛ حيث جمع فيه محاسِنَ ما قَبْلَه وزاده من الكمالاتِ ما ليس في غيرِه؛ فلهذا جعله شاهدًا وأمينًا، وحاكمًا عليها كُلِّها) .</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>يتناول الكتب السابقة (التوراة والإنجيل) ودخول التحريف عليها، وجمهورنا قد يكون غير مسلم.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>1) هل المقطع بحدوده مناسب لسائل غير مسلم يسأل «هل القرآن مثل الإنجيل؟»
+2) هل يُبقى سطر «قد دخله التحريف والتبديل» أم يُقصّ المقطع عند «…وحاكماً عليها كلها»؟</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"موافق,موافق بتعديل,غير موافق"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1978,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V33"/>
+  <dimension ref="A1:V35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2200,7 +2248,7 @@
       </c>
       <c r="V2" s="12" t="n"/>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="170" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>ق-02</t>
@@ -2223,38 +2271,69 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>الدرر 1375</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr"/>
-      <c r="J3" s="6" t="inlineStr"/>
+          <t>فضائل القرآن — المبحث الأول: من فضائل القرآن أنه هدى للمتقين — https://dorar.net/aqeeda/1376</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>قال اللهُ تعالى: ﴿ذَلِكَ الكِتَابُ لَا رَيْبَ فِيهِ هُدًى لِلْمُتَّقِينَ﴾ [البقرة: 2] .
+[…]
+وقال اللهُ عَزَّ وجَلَّ: ﴿إِنَّ هَذَا القُرْآنَ يَهْدِي لِلَّتِي هِيَ أَقْوَمُ﴾ [الإسراء: 9] .
+قال السَّعديُّ: (يخبرُ تعالى عن شَرَفِ القُرْآنِ وجَلالتِه وأنَّه يَهْدِي لِلَّتِي هِيَ أَقْوَمُ أي: أعدَلُ وأعلى من العقائدِ والأعمالِ والأخلاقِ، فمن اهتدى بما يدعو إليه القُرْآنُ كان أكمَلَ النَّاسِ وأقوَمَهم وأهداهم في جميعِ أُمورِه)</t>
+        </is>
+      </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>مكانة القرآن وفضله</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr"/>
-      <c r="O3" s="6" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr"/>
+          <t>مكانة القرآن: أنه هدى للمتقين، ويهدي للتي هي أقوم في العقائد والأعمال والأخلاق.</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>ما مكانة القرآن عند المسلمين؟ | لماذا يعظّم المسلمون القرآن؟ | ما فائدة القرآن للإنسان؟ | لماذا يقرأ المسلمون القرآن كثيراً؟</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>البقرة 2؛ الإسراء 9 (تُعرض من المصحف). في كلام السعدي جزء آية دون علامة.</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="n"/>
+      <c r="Q3" s="6" t="n"/>
+      <c r="R3" s="6" t="n"/>
       <c r="S3" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T3" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr">
+        <is>
+          <t>قصّ واحد «[…]»: حذفت كلام ابن كثير الطويل (فيه ثلاث آيات) للاختصار.</t>
+        </is>
+      </c>
       <c r="U3" s="9">
         <f>IF(A3="","",IF(J3="","لم يُستخرج بعد",IF(OR(M3="ج",M3="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D3,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D3,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B3="",E3="",K3="",M3="",N3=""),"بيانات ناقصة",IF(P3&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q3="","المراجعة غير موثقة",IF(AND(N3="نعم",R3="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N3="نعم",R3&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S3&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="170" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ق-03</t>
@@ -2277,35 +2356,74 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>الدرر 1392</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
+          <t>خصائص القرآن — المبحث الثامن: هيمنته على الكتب السابقة — https://dorar.net/aqeeda/1417</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>قال اللهُ تعالى: ﴿وَأَنْزَلْنَا إِلَيْكَ الْكِتَابَ بِالْحَقِّ مُصَدِّقًا لِمَا بَيْنَ يَدَيْهِ مِنَ الْكِتَابِ وَمُهَيْمِنًا عَلَيْهِ فَاحْكُمْ بَيْنَهم بِمَا أَنْزَلَ اللَّهُ﴾ [المائدة: 48] .
+أي: وأنزلْناه شاهدًا للكتُبِ الإلهيَّةِ السَّابقةِ بصِدقها، وموافقًا لها، ومطابِقًا لأخبارِها وأصولِ شرائِعِها، وفي وجودِه أيضًا دَلالةٌ على صِدقِها؛ لأنَّها أَخبرتْ بنُزولِ القُرآنِ. وأنزلْناه أمينًا على الكتُبِ الإلهيَّةِ السَّابقةِ، حافظًا لها، مُشتَمِلًا على ما اشتملَتْ عليه الكتُبُ السَّابقَةُ وزيادةٍ، وناسِخًا لها، وحاكمًا عليها كلِّها، فما شهِد له القُرْآنُ منها بالصِّدقِ فهو مقبولٌ، وما شهِد له بالردِّ فهو مردودٌ، قد دخلَه التحريفُ والتبديلُ، وإلَّا فلو كان مِن عِندِ اللهِ تعالى لم يُخالِفْه. وما دام أنَّ هذه هي حالُ القُرْآنِ؛ فاحكُمْ إذنْ -يا محمَّدُ- بينَ أهلِ الكِتاب وغيرِهم بهذا القُرْآنِ العظيمِ في كلِّ ما احتَكموا فيه إليك .
+[…]
+وقال ابنُ كثيرٍ: (جعل اللهُ هذا الكِتابَ العظيمَ الذي أنزله آخِرَ الكُتُبِ وخاتِمَها وأشمَلَها وأعظَمَها وأكمَلَها؛ حيث جمع فيه محاسِنَ ما قَبْلَه وزاده من الكمالاتِ ما ليس في غيرِه؛ فلهذا جعله شاهدًا وأمينًا، وحاكمًا عليها كُلِّها) .</t>
+        </is>
+      </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>خصائص القرآن: مصدّق لما قبله ومهيمن عليه</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
-      <c r="N4" s="6" t="inlineStr"/>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="6" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
+          <t>صلة القرآن بالكتب السابقة: مصدّق لها ومهيمن عليها، أمين وشاهد وحاكم عليها، وهو آخر الكتب وخاتمها.</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>هل القرآن مثل الإنجيل عند المسيحيين؟ | ما علاقة القرآن بالتوراة والإنجيل؟ | ما معنى أن القرآن مهيمن؟</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>ب</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>المائدة 48 (تُعرض من المصحف)</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6">
+        <f>IF(للمختص!H15="","",للمختص!H15)</f>
+        <v/>
+      </c>
       <c r="S4" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>قصّ «[…]»: حذفت أقوال السلف المتعددة وكلام ابن تيمية وابن باز وابن عثيمين للطول. حساس لأنه يتناول الكتب السابقة والتحريف أمام جمهور قد يكون غير مسلم.</t>
+        </is>
+      </c>
       <c r="U4" s="9">
         <f>IF(A4="","",IF(J4="","لم يُستخرج بعد",IF(OR(M4="ج",M4="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D4,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D4,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B4="",E4="",K4="",M4="",N4=""),"بيانات ناقصة",IF(P4&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q4="","المراجعة غير موثقة",IF(AND(N4="نعم",R4="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N4="نعم",R4&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S4&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>يتناول الكتب السابقة (التوراة والإنجيل) ودخول التحريف عليها، وجمهورنا قد يكون غير مسلم.</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1">
@@ -2618,7 +2736,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="170" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>ق-09</t>
@@ -2636,33 +2754,67 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>م-03</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="6" t="inlineStr"/>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>فضائل القرآن — المبحث الثاني: إنزاله في شهر رمضان، أول المبحث — https://dorar.net/aqeeda/1378</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>إذا كان شَهرُ رَمَضانَ قد نال هذه المزِيَّةَ بسبب نزول القُرْآنِ فيه، فما الظَّنُّ بشَرَفِ القُرْآنِ المنَزَّلِ نفسِه؟!
+قال اللهُ سُبحانَه: ﴿شَهْرُ رَمَضَانَ الَّذِي أُنْزِلَ فِيهِ القُرْآَنُ هُدًى لِلنَّاسِ وَبَيِّنَاتٍ مِنَ الهُدَى وَالفُرْقَانِ﴾ [البقرة: 185] .
+قال البقاعيُّ: (في مَدْحِه بإنزالِه فيه مَدحٌ للقُرْآنِ به) .</t>
+        </is>
+      </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>بداية نزول القرآن ونزوله مفرّقاً</t>
-        </is>
-      </c>
-      <c r="L10" s="6" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
-      <c r="N10" s="6" t="inlineStr"/>
-      <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="6" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr"/>
+          <t>متى نزل القرآن: نزل في شهر رمضان، وصار نزوله فيه مزيّة لهذا الشهر.</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>متى نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما علاقة القرآن برمضان؟</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>البقرة 185 (تُعرض من المصحف)</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="n"/>
+      <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T10" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>أول المبحث فقط (ثلاث فقرات). لا يذكر نزوله مفرّقاً؛ ذلك في ق-37.</t>
+        </is>
+      </c>
       <c r="U10" s="9">
         <f>IF(A10="","",IF(J10="","لم يُستخرج بعد",IF(OR(M10="ج",M10="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D10,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D10,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B10="",E10="",K10="",M10="",N10=""),"بيانات ناقصة",IF(P10&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q10="","المراجعة غير موثقة",IF(AND(N10="نعم",R10="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N10="نعم",R10&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S10&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
@@ -3798,7 +3950,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>أساسي</t>
+          <t>إضافي</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -4767,8 +4919,174 @@
       </c>
       <c r="V33" s="12" t="n"/>
     </row>
+    <row r="34" ht="170" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>ق-36</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>فضائل القرآن — المبحث الثامن: الوعد بالثواب على قراءته ومدارسته — https://dorar.net/aqeeda/1390</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>عن أبي هُرَيرةَ رَضِيَ اللهُ عنه أنَّ رَسولَ اللهِ صلَّى اللهُ عليه وسلَّم قال: ((وما اجتمع قومٌ في بيتٍ من بُيوتِ اللهِ يَتْلون كِتابَ اللهِ ويتدارسونَه بينهم، إلَّا نزلت عليهم السَّكينةُ، وغَشِيَتهم الرَّحمةُ، وحَفَّتْهم المَلائِكةُ، وذكرهم اللهُ فيمَن عِندَه )) .
+[…]
+قال ابنُ عُثَيمين: (هذا القُرْآنُ له فضائلُ عظيمةٌ؛ فضائِلُ عامَّةٌ، وفضائِلُ في آياتٍ وسُوَرٍ خاصَّةٍ؛ مثلًا الفاتحةُ هي السَّبعُ المثاني وهي أمُّ الكِتابِ، آيةُ الكرسيِّ هي أعظَمُ آيةٍ في كِتابِ الله، وهَلُمَّ جَرًّا، هناك آياتٌ أو سُوَرٌ لها فضلٌ خاصٌّ، أمَّا القُرْآنُ عمومًا فله أيضًا فضائِلُ عامَّةٌ، وهذا يوجِبُ علينا أن نحرِصَ غايةَ الحِرصِ على تلاوةِ كِتابِ اللهِ عَزَّ وجَلَّ ليلًا ونهارًا) .</t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>فضل تلاوة القرآن ومدارسته، والحثّ على تلاوته ليلاً ونهاراً.</t>
+        </is>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>ما فضل قراءة القرآن؟ | لماذا أقرأ القرآن؟ | هل في قراءة القرآن أجر؟ | ما فائدة الاجتماع على القرآن؟</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>حديث أبي هريرة: «وما اجتمع قوم في بيت من بيوت الله…» — صحيح مسلم (2699)؛ يُتحقق من رقمه في الموسوعة الحديثية</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="n"/>
+      <c r="Q34" s="6" t="n"/>
+      <c r="R34" s="6" t="n"/>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>قصّ «[…]»: حذفت شرح المنح الأربع للطول، وأبقيت الحديث وكلام ابن عثيمين. يجيب عن «لماذا أقرأ» لا عن «من أين أبدأ».</t>
+        </is>
+      </c>
+      <c r="U34" s="9">
+        <f>IF(A34="","",IF(J34="","لم يُستخرج بعد",IF(OR(M34="ج",M34="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D34,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D34,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B34="",E34="",K34="",M34="",N34=""),"بيانات ناقصة",IF(P34&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q34="","المراجعة غير موثقة",IF(AND(N34="نعم",R34="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N34="نعم",R34&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S34&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="170" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>ق-37</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>إضافي</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>خصائص القرآن — المبحث الثامن، من كلام ابن كثير في نزول القرآن منجّماً — https://dorar.net/aqeeda/1417</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>[قال ابن كثير:] (… القُرْآنِ الذي شرَّفه اللهُ على كُلِّ كِتابٍ أنزله، وجعله مُهَيمِنًا عليه وناسِخًا له وخاتمًا له؛ لأنَّ كُلَّ الكُتُبِ المتقَدِّمةِ نزلت إلى الأرضِ جملةً واحدةً، وهذا القُرْآنُ نزل مُنجَّمًا بحسَبِ الوقائِعِ؛ لشِدَّةِ الاعتناءِ به وبمن أُنزِل عليه، فكُلُّ مرَّةٍ كنُزولِ كِتابٍ مِن الكُتُبِ المتقَدِّمةِ) .</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>نزول القرآن منجّماً (مفرّقاً) بحسب الوقائع، بخلاف الكتب السابقة التي نزلت جملة واحدة.</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>هل نزل القرآن مرة واحدة؟ | لماذا نزل القرآن مفرّقاً؟ | كم مرة نزل القرآن؟</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="6" t="n"/>
+      <c r="R35" s="6" t="n"/>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>من وسط كلام ابن كثير: أضفت «[قال ابن كثير:]» بين معقوفين لأن النص في المصدر يبدأ بـ«وقال أيضاً»، و«(…» علامة بتر من أوله.</t>
+        </is>
+      </c>
+      <c r="U35" s="9">
+        <f>IF(A35="","",IF(J35="","لم يُستخرج بعد",IF(OR(M35="ج",M35="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D35,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D35,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B35="",E35="",K35="",M35="",N35=""),"بيانات ناقصة",IF(P35&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q35="","المراجعة غير موثقة",IF(AND(N35="نعم",R35="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N35="نعم",R35&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S35&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V33"/>
+  <autoFilter ref="A1:V35"/>
   <conditionalFormatting sqref="N2:N60">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N2="نعم"</formula>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'المقاطع'!$A$1:$V$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -719,6 +719,13 @@
       <c r="A23" t="inlineStr">
         <is>
           <t>v11: أُضيفت 5 مقاطع من الدرر: ق-02 مكانة القرآن، ق-03 هيمنته على الكتب السابقة (حساس)، ق-09 نزوله في رمضان، ق-36 فضل تلاوته، ق-37 نزوله منجّماً. ق-18 صار إضافياً.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v12: من صفحة الدرر 1411: ق-08 كيف كان يأتي الوحي (أساسي ح2)، ق-38 الحفظ زمن النبوة (بديل ح3)، ق-39 فضل تعلم القرآن (إضافي ح6).</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2686,7 +2693,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="170" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ق-08</t>
@@ -2704,33 +2711,67 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>م-03</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>خصائص القرآن — المبحث السادس، المطلب الأول: حفظ القرآن في عهد النبوة، الوجه 1 (طريقة نزول الوحي) — https://dorar.net/aqeeda/1411</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>1- الطريقةُ التي كان يَنزِلُ بها الوَحيُ:
+كان الوَحيُ يَنزِلُ على النَّبيِّ صلَّى اللهُ عليه وسلَّم على هيئةٍ تكون أدعى إلى حِفْظِه وضَبْطِه.
+عن عائِشةَ رَضِيَ اللهُ عنها أنَّ الحارِثَ بنَ هشامٍ رَضِيَ اللهُ عنه سأل رسولَ الله صلَّى اللهُ عليه وسلَّم فقال: ((يا رسولَ اللهِ، كيف يأتيك الوَحيُ؟ فقال رَسولُ اللهِ صلَّى اللهُ عليه وسلَّم: أحيانًا يأتيني مِثْلَ صَلصَلةِ الجَرَسِ، وهو أشَدُّه عَلَيَّ، فيَفصِمُ عَنِّي وقد وَعَيتُ عنه ما قال، وأحيانًا يتمَثَّلُ لي المَلَكُ رَجُلًا، فيُكَلِّمُني، فأعي ما يقولُ )) .</t>
+        </is>
+      </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>الوحي: كيف كان يأتي النبي ﷺ</t>
-        </is>
-      </c>
-      <c r="L9" s="6" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
-      <c r="N9" s="6" t="inlineStr"/>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="6" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
+          <t>كيف كان الوحي يأتي النبي ﷺ: أحياناً مثل صلصلة الجرس وهو أشدّه عليه، وأحياناً يتمثّل له الملك رجلاً فيكلّمه.</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>كيف كان الوحي يأتي النبي؟ | ما هو الوحي؟ | كيف وصل القرآن لمحمد؟ | كيف كان جبريل ينزل بالقرآن؟</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>حديث عائشة في سؤال الحارث بن هشام: صحيح البخاري (2)، وصحيح مسلم (2333) — يُتحقق من الرقمين في الموسوعة الحديثية</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
       <c r="S9" s="6" t="inlineStr">
         <is>
-          <t>لم يُستخرج</t>
-        </is>
-      </c>
-      <c r="T9" s="6" t="inlineStr"/>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>الوجه الأول فقط بلا شرح القرطبي (للطول).</t>
+        </is>
+      </c>
       <c r="U9" s="9">
         <f>IF(A9="","",IF(J9="","لم يُستخرج بعد",IF(OR(M9="ج",M9="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D9,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D9,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B9="",E9="",K9="",M9="",N9=""),"بيانات ناقصة",IF(P9&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q9="","المراجعة غير موثقة",IF(AND(N9="نعم",R9="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N9="نعم",R9&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S9&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
         <v/>
@@ -5085,8 +5126,181 @@
         <v/>
       </c>
     </row>
+    <row r="36" ht="170" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>ق-38</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>ح3</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>إضافي</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>خصائص القرآن — المبحث السادس، المطلب الأول: حفظ القرآن في عهد النبوة، الوجهان 3 و6 — https://dorar.net/aqeeda/1411</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>للحِفظِ في عَهدِ النُّبُوَّةِ عِدَّةُ أوجُهٍ؛ منها:
+[…]
+3- كِتابةُ الوَحيِ ومُقابلَتُه:
+قال الحارِثُ المحاسبيُّ: (كِتابةُ القُرْآنِ ليست مُحدَثةً؛ فإنَّه صلَّى اللهُ عليه وسلَّم كان يأمُرُ بكِتابتِه ولكِنَّه كان مُفَرَّقًا في الرِّقاعِ والأكتافِ والعُسُبِ  ، وإنما أمر الصِّدِّيقُ بنَسْخِها من مكانٍ إلى مكانٍ، وكان ذلك بمَنْزِلةِ أوراقٍ وُجِدَت في بيتِ رَسولِ الله صلَّى اللهُ عليه وسلَّم فيها القُرْآنُ مُنتَشِرٌ، فجَمَعها جامِعٌ وربطَها بخَيطٍ حتى لا يَضِيعَ منها شَيءٌ) .
+وقال أبو عَمرٍو الدَّاني: (إنَّ رَسولَ اللهِ صلَّى اللهُ عليه وسلَّم سَنَّ جمعَ القُرْآنِ وكِتابتَه، وأمر بذلك وأملاه على كَتَبَتِه، وأنَّه صلَّى اللهُ عليه وسلَّم لم يَمُتْ حتى حَفِظَ جميعَ القُرْآنِ جماعةٌ من أصحابِه) .
+[…]
+6- قُوَّةُ الحافِظةِ عند العَرَبِ:
+كان العَرَبُ أهلَ حافِظةٍ لا تكادُ تُخطِئُ، وذاكِرةٍ لا يكادُ يَعزُبُ عنها شيءٌ، وخاصَّةً أنَّ القُرْآنَ جاء بأسلوبٍ بارعٍ، وبيانٍ رَفيعٍ؛ ممَّا جعله أحرى لحِفْظِه، والاهتمامِ به، حتى كَثُر آخِذوه صدرًا وسَطرًا.</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>كيف حُفظ القرآن زمن النبي ﷺ: كان يأمر بكتابته فكُتب مفرّقاً في الرقاع والأكتاف، وحفظه جماعة من أصحابه، وكان العرب أهل حافظة قوية.</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>كيف حُفظ القرآن زمن النبي؟ | هل كُتب القرآن في حياة النبي؟ | كيف استطاع الصحابة حفظ القرآن؟</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="n"/>
+      <c r="Q36" s="6" t="n"/>
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>بديل لـق-11 بنص غير جدلي. قصّان «[…]»: حذفت الوجوه 1 و2 و4 و5 (الأول في ق-08، والخامس في ق-39).</t>
+        </is>
+      </c>
+      <c r="U36" s="9">
+        <f>IF(A36="","",IF(J36="","لم يُستخرج بعد",IF(OR(M36="ج",M36="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D36,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D36,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B36="",E36="",K36="",M36="",N36=""),"بيانات ناقصة",IF(P36&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q36="","المراجعة غير موثقة",IF(AND(N36="نعم",R36="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N36="نعم",R36&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S36&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="170" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>ق-39</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>إضافي</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>م-02</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>خصائص القرآن — المبحث السادس، المطلب الأول، الوجه 5: الحض على تعلم القرآن وتعليمه — https://dorar.net/aqeeda/1411</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>5- الحَضُّ على تعَلُّمِ القُرْآنِ وتعليمِه:
+عن عُثمانَ بنِ عَفَّانَ رَضِيَ اللهُ عنه، عن النَّبيِّ صلَّى اللهُ عليه وسلَّم قال: ((خيرُكم من تعلَّم القُرْآنَ وعَلَّمه )) .
+وكان النَّبيُّ صلَّى اللهُ عليه وسلَّم يحُثُّ أصحابَه رَضِيَ اللهُ عنهم على تعَلُّمِ القُرْآنِ وتعليمِه، وحِفْظِه وتحفيظِه، وكان يُقَدِّمُ أكثَرَهم أخذًا للقُرْآنِ في إمامةِ الصَّلَواتِ، وقيادةِ السَّرايا.</t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>الحثّ على تعلّم القرآن وتعليمه: «خيركم من تعلّم القرآن وعلّمه»، وكان النبي ﷺ يقدّم أكثر أصحابه أخذاً للقرآن.</t>
+        </is>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>ما فضل تعلّم القرآن؟ | هل أتعلّم القرآن مع غيري؟ | خيركم من تعلم القرآن وعلمه</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>حديث عثمان: «خيركم من تعلّم القرآن وعلّمه» — صحيح البخاري (5027) — يُتحقق من الرقم</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>جاهز للمراجعة</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>الوجه الخامس دون كلام الباقلاني (للطول).</t>
+        </is>
+      </c>
+      <c r="U37" s="9">
+        <f>IF(A37="","",IF(J37="","لم يُستخرج بعد",IF(OR(M37="ج",M37="د"),"المستوى لا يُنشر",IF(OR(IFERROR(INDEX(المصادر!$E$2:$E$20,MATCH(D37,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"معروضة",IFERROR(INDEX(المصادر!$F$2:$F$20,MATCH(D37,المصادر!$A$2:$A$20,0)),"")&lt;&gt;"نعم"),"المصدر غير معتمد",IF(OR(B37="",E37="",K37="",M37="",N37=""),"بيانات ناقصة",IF(P37&lt;&gt;"نعم","لم يجتز الفحوص",IF(Q37="","المراجعة غير موثقة",IF(AND(N37="نعم",R37="موافق بتعديل"),"بانتظار تنفيذ التعديل",IF(AND(N37="نعم",R37&lt;&gt;"موافق"),"بانتظار رأي المختص",IF(S37&lt;&gt;"معتمد","لم يُعتمد","قابل للنشر"))))))))))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V35"/>
+  <autoFilter ref="A1:V37"/>
   <conditionalFormatting sqref="N2:N60">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$N2="نعم"</formula>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخص" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'للمراجعة'!$A$1:$V$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'للمراجعة'!$A$1:$V$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'المقاطع'!$A$1:$S$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V42"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1794,46 +1794,88 @@
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
     </row>
-    <row r="14" ht="48" customHeight="1">
+    <row r="14" ht="150" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>و-01</t>
+          <t>ق-10</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>أعلى كل صفحة</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 4: المكي والمدني — الفرق بين المكي والمدني (ص 60 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>الفرق بين المكي والمدني</t>
+        </is>
+      </c>
       <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>ما الفرق بين المكي والمدني؟ | ما معنى سورة مكية؟ | ما معنى سورة مدنية؟</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>«دليل» أداة تستعين بالذكاء الاصطناعي لتختار لك مقطعاً من مصادر إسلامية معتمدة راجعها مختص. لا تكتب إجابات من عندها، وقد تخطئ في الاختيار.</t>
-        </is>
-      </c>
-      <c r="L14" s="6" t="n"/>
-      <c r="M14" s="6" t="n"/>
-      <c r="N14" s="6" t="n"/>
+          <t>للعلماء في الفرق بين المكي والمدني ثلاثة آراء اصطلاحية، كل رأي منها بُنِيَ على اعتبار خاص.
+الأول: اعتبار زمن النزول، فالمكي: ما نزل قبل الهجرة وإن كان بغير مكة، والمدني: ما نزل بعد الهجرة وإن كان بغير المدينة، فما نزل بعد الهجرة ولو بمكة، أو عرفة: مدني، كالذي نزل عام الفتح، كقوله تعالى: ﴿إِنَّ اللَّهَ يَأْمُرُكُمْ أَنْ تُؤَدُّوا الْأَمَانَاتِ إِلَى أَهْلِهَا﴾ [النساء: 58]، فإنها نزلت بمكة في جوف الكعبة عام الفتح الأعظم، أو نزل بحجة الوداع كقوله تعالى: ﴿الْيَوْمَ أَكْمَلْتُ لَكُمْ دِينَكُمْ وَأَتْمَمْتُ عَلَيْكُمْ نِعْمَتِي وَرَضِيتُ لَكُمُ الْإِسْلَامَ دِينًا﴾ [المائدة: 3]، وهذا الرأي أولى من الرأيين بعده لحصره واطراده.
+[…]</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>معنى «مكي» و«مدني»: المكي ما نزل قبل الهجرة، والمدني ما نزل بعدها، وهو أرجح الآراء الثلاثة.</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>ما معنى سورة مكية ومدنية؟ | يعني إيش مكية؟ | ليش مكتوب على السورة مدنية؟ | هل المكي ما نزل في مكة فقط؟</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P14" s="6" t="n"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>النساء 58 (جزء)؛ المائدة 3 (جزء) — تُعرض من المصحف.</t>
+        </is>
+      </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>أخذت الرأي الأول (الذي رجّحه المؤلف) كاملاً، وقصصت الرأيين الآخرين «[…]» لأنهما يربكان المبتدئ. حذفت أرقام الحواشي.</t>
         </is>
       </c>
       <c r="R14" s="6" t="n"/>
@@ -1842,46 +1884,88 @@
       <c r="U14" s="8" t="n"/>
       <c r="V14" s="8" t="n"/>
     </row>
-    <row r="15" ht="48" customHeight="1">
+    <row r="15" ht="150" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>و-02</t>
+          <t>ق-05</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>بعد كل جزء معروض</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 4: المكي والمدني — مدخل الفصل (ص 49–50 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>خصائص الآيات المكية والمدنية</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>ما موضوعات القرآن؟ | عن ماذا يتكلم القرآن؟ | ما الرسالة الأساسية في القرآن؟</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>هل أجاب هذا عن سؤالك؟  [نعم] [جزئياً] [لا]</t>
-        </is>
-      </c>
-      <c r="L15" s="6" t="n"/>
-      <c r="M15" s="6" t="n"/>
-      <c r="N15" s="6" t="n"/>
+          <t>والذي يقرأ القرآن الكريم يجد للآيات المكية خصائص ليست للآيات المدنية في وقعها ومعانيها، وإن كانت الثانية مبنية على الأولى في الأحكام والتشريع.
+[…] نزل الوحي المكي قوارع زاجرة، وشهبًا منذرة، وحججًا قاطعة، يحطم وثنيتهم في العقيدة، ويدعوهم إلى توحيد الألوهية والربوبية، ويهتك أستار فسادهم، ويسَفِّه أحلامهم، ويقيم دلائل النبوة، ويضرب الأمثلة للحياة الآخرة وما فيها من جنة ونار، ويتحداهم -على فصاحتهم- بأن يأتوا بمثل القرآن، ويسوق إليهم قصص المكذبين الغابرين عبرة وذكرى […]
+وحين تكونت الجماعة المؤمنة بالله وملائكته وكتبه ورسله واليوم الآخر وبالقدر خيره وشره، وامتُحنت في عقيدتها بأذى المشركين فصبرت وهاجرت بدينها مؤثرة ما عند الله على متع الحياة -حين تكونت هذه الجماعة- نرى الآيات المدنية طويلة المقاطع، تتناول أحكام الإسلام وحدوده، وتدعو إلى الجهاد والاستشهاد في سبيل الله، وتفصل أصول التشريع، وتضع قواعد المجتمع، وتحدد روابط الأسرة، وصلات الأفراد، وعلاقات الدول والأمم، كما تفضح المنافقين وتكشف دخيلتهم، وتجادل أهل الكتاب وتلجم أفواههم -وهذا هو الطابع العام للقرآن المدني.</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>أبرز موضوعات القرآن: التوحيد، ودلائل النبوة، والآخرة والجنة والنار، وقصص الأمم السابقة، ثم الأحكام وقواعد المجتمع والأسرة.</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>عن ماذا يتكلم القرآن؟ | ما الرسالة الأساسية في القرآن؟ | هل القرآن كتاب أحكام فقط؟ | هل يتكلم القرآن عن يوم القيامة؟ | ماذا يطلب القرآن من الإنسان؟</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P15" s="6" t="n"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>قصّان «[…]»: (1) وصف حال المشركين وقولهم مع آيتين، (2) وصف ألفاظ المكي وأساليبه. يغطي هذا المقطع وحده ق-05 وق-07 المخططين (التوحيد، والآخرة، والقيم)، فحذفت ق-07 من «الناقص».</t>
         </is>
       </c>
       <c r="R15" s="6" t="n"/>
@@ -1890,46 +1974,92 @@
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="8" t="n"/>
     </row>
-    <row r="16" ht="48" customHeight="1">
+    <row r="16" ht="150" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>و-03</t>
+          <t>ق-06</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>بعد «جزئياً»</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 21: قصص القرآن — معنى القصص، وأنواعه، وفوائده (ص 316–317 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>قصص القرآن</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>هل في القرآن قصص؟ | ما قصص القرآن؟ | هل يذكر القرآن الأنبياء؟</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>ما الذي بقي دون إجابة؟ اكتبه بكلماتك.</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="n"/>
-      <c r="M16" s="6" t="n"/>
-      <c r="N16" s="6" t="n"/>
+          <t>وقصص القرآن: أخباره عن أحوال الأمم الماضية، والنبوات السابقة، والحوادث الواقعة - وقد اشتمل القرآن على كثير من وقائع الماضي، وتاريخ الأمم، وذكر البلاد والديار، وتتبع آثار كل قوم، وحكى عنهم صورة ناطقة لما كانوا عليه.
+والقصص في القرآن ثلاثة أنواع:
+النوع الأول: قصص الأنبياء، وقد تضمن دعوتهم إلى قومهم، والمعجزات التي أيدهم الله بها، وموقف المعاندين منهم، ومراحل الدعوة وتطورها وعاقبة المؤمنين والمكذبين، كقصص نوح، وإبراهيم، وموسى، وهارون، وعيسى، ومحمد، وغيرهم من الأنبياء والمرسلين، عليهم جميعًا أفضل الصلاة والسلام.
+[…]
+النوع الثالث: قصص يتعلق بالحوادث التي وقعت في زمن رسول الله -صلى الله عليه وسلم- كغزوة بدر وأحد في سورة آل عمران، وغزوة حنين وتبوك في التوبة، وغزوة الأحزاب في سورة الأحزاب، والهجرة، والإسراء، ونحو ذلك.
+وللقصص القرآني فوائد نجمل أهمها فيما يأتي:
+1- إيضاح أسس الدعوة إلى الله، وبيان أصول الشرائع التي بعث بها كل نبي: ﴿وَمَا أَرْسَلْنَا مِنْ قَبْلِكَ مِنْ رَسُولٍ إِلَّا نُوحِي إِلَيْهِ أَنَّهُ لَا إِلَهَ إِلَّا أَنَا فَاعْبُدُونِ﴾ [الأنبياء: 25].</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>هل في القرآن قصص؟ نعم: قصص الأنبياء، وأحداث زمن النبي ﷺ، والغاية منها بيان أسس الدعوة إلى التوحيد.</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>هل القرآن فيه قصص؟ | هل يذكر القرآن موسى وعيسى؟ | ليش القرآن يحكي قصص الأنبياء؟ | هل قصص القرآن حقيقية؟</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P16" s="6" t="n"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>الأنبياء 25 (كاملة) — تُعرض من المصحف.</t>
+        </is>
+      </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>قصّ واحد «[…]»: النوع الثاني (فيه عبارة «لم تثبت ثبوتهم» قد تُفهم خطأً، ويحسن عرضها مع شرح). من الفوائد أخذت الأولى فقط لأن البقية لم ترد في النسخة الرقمية.</t>
         </is>
       </c>
       <c r="R16" s="6" t="n"/>
@@ -1938,46 +2068,91 @@
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17" ht="150" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>و-04</t>
+          <t>ق-15</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>فوق كل مقطع (يُملأ من السجل)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 8: جمع القرآن وترتيبه — ترتيب الآيات، وسور القرآن وآياته (ص 140، 145 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>السورة والآية وعدد السور</t>
+        </is>
+      </c>
       <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>ما الفرق بين السورة والآية؟ | كم عدد سور القرآن؟ | كم عدد آيات القرآن؟</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>يجيب هذا المقطع عن: {يجيب_عن}</t>
-        </is>
-      </c>
-      <c r="L17" s="6" t="n"/>
-      <c r="M17" s="6" t="n"/>
-      <c r="N17" s="6" t="n"/>
+          <t>القرآن سور وآيات منها القصار والطوال، والآية: هي الجملة من كلام الله المندرجة في سورة من القرآن، والسورة: هي الجملة من آيات القرآن ذات المطلع والمقطع.
+[…]
+وتعداد السور: مائة وأربع عشرة سورة، وقيل: وثلاث عشرة بجعل الأنفال وبراءة سورة واحدة.
+أما تعداد الآيات فستة آلاف ومائتا آية، واختلفوا فيما زاد عن ذلك.
+وأطول الآيات آية الدَّيْن، وأطول السور سورة البقرة.
+وهذه التجزئة تيسر على الناس الحفظ، وتحملهم على الدراسة، وتشعر القارئ لسورة من السور بأنه قد أخذ قسطاً وافيًا وطائفة مستقلة من أصول دينه وأحكام شريعته.</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>ما السورة وما الآية؟ وعدد سور القرآن 114 سورة، وآياته ستة آلاف ومئتان وزيادة.</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>كم عدد سور القرآن؟ | ما الفرق بين السورة والآية؟ | كم آية في القرآن؟ | ما أطول سورة؟</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P17" s="6" t="n"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>جمعت فقرتين من موضعين: تعريف الآية والسورة (ص 140) ثم العدد (ص 145)، وبينهما «[…]». أبقيت «وقيل: وثلاث عشرة» كما في المصدر.</t>
         </is>
       </c>
       <c r="R17" s="6" t="n"/>
@@ -1986,94 +2161,185 @@
       <c r="U17" s="8" t="n"/>
       <c r="V17" s="8" t="n"/>
     </row>
-    <row r="18" ht="48" customHeight="1">
+    <row r="18" ht="150" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>و-05</t>
+          <t>ق-16</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>تحت وصف «يجيب عن»</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 8: جمع القرآن وترتيبه — ترتيب الآيات وترتيب السور (ص 140–145 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>ترتيب الآيات والسور</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>من رتّب القرآن؟ | هل ترتيب المصحف حسب النزول؟ | لماذا السور مرتبة هكذا؟</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>وصف مساعد كُتب بمساعدة الذكاء الاصطناعي وراجعه صاحب المشروع. النص المعتمد هو المقتبس.</t>
-        </is>
-      </c>
-      <c r="L18" s="6" t="n"/>
-      <c r="M18" s="6" t="n"/>
-      <c r="N18" s="6" t="n"/>
+          <t>وترتيب الآيات في القرآن الكريم توقيفي عن رسول الله -صلى الله عليه وسلم- وحكى بعضهم الإجماع على ذلك […] فقد كان جبريل يتنزل بالآيات على رسول الله -صلى الله عليه وسلم- ويرشده إلى موضعها من السورة أو الآيات التي نزلت قبل، فيأمر الرسول كتبة الوحي بكتابتها في موضعها ويقول لهم: ضعوا هذه الآيات في السورة التي يُذكر فيها كذا أو كذا، أو ضعوا آية كذا في موضع كذا […]
+وكان جبريل يعارض رسول الله -صلى الله عليه وسلم- بالقرآن كل عام مرة في رمضان، وعارضه في العام الأخير من حياته مرتين، وكان ذلك العرض على الترتيب المعروف الآن.
+[…]
+وبهذا يترجح أن ترتيب السور توقيفي كترتيب الآيات.</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>لماذا ليس ترتيب المصحف بحسب النزول؟ لأن ترتيب الآيات بأمر النبي ﷺ عن جبريل، والراجح أن ترتيب السور كذلك.</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>ليش السور مو مرتبة حسب نزولها؟ | من رتب سور القرآن؟ | هل ترتيب الآيات من النبي؟ | ليش البقرة أول القرآن مع إنها مدنية؟</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P18" s="6" t="n"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="n"/>
+          <t>ثلاثة قصوص «[…]»: أسماء من حكى الإجماع، والأحاديث والآثار (ستحتاج تخريجاً)، ومناقشة الآراء الثلاثة في ترتيب السور. الخلاف في ترتيب السور مذكور في المصدر، والمقطع يعرض الراجح فقط.</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>المصدر يذكر خلافاً في ترتيب السور ويرجّح التوقيف. هل عرض الراجح وحده مناسب للمبتدئ؟</t>
+        </is>
+      </c>
       <c r="S18" s="8" t="n"/>
       <c r="T18" s="8" t="n"/>
       <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
     </row>
-    <row r="19" ht="48" customHeight="1">
+    <row r="19" ht="150" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ست-01</t>
+          <t>ق-19</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>التباس بين ح1 وح7</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 23: التفسير والتأويل — مدخل الفصل، ومعنى التفسير، وشرف التفسير (ص 334، 339 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>معنى التفسير والحاجة إليه</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>ما التفسير؟ | كيف أفهم القرآن؟ | ما معنى تفسير القرآن؟</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>هل تريد تعريفاً بالقرآن ومكانته، أم الأسباب التي تجعل المسلمين يؤمنون أنه من عند الله؟</t>
-        </is>
-      </c>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
+          <t>ولا يستوي الناس جميعًا في فهم ألفاظه وعباراته مع وضوح بيانه وتفصيل آياته، فإن تفاوت الإدراك بينهم أمر لا مراء فيه فالعامي يدرك من المعاني ظاهرها ومن الآيات مجملها، والذكي المتعلم يستخرج منها المعنى الرائع. وبين هذا وذاك مراتب فهم شتى، فلا غرو أن يجد القرآن من أبناء أمته اهتمامًا بالغًا في الدراسة لتفسير غريب، أو تأويل تركيب.
+[…]
+وقال الزركشي: التفسير: علم يُفهم به كتاب الله المنزل على نبيه محمد, صلى الله عليه وسلم: وبيان معانيه، واستخراج أحكامه وحكمه.
+[…]
+والتفسير من أجلِّ علوم الشريعة وأرفعها قدرًا، وهو أشرف العلوم موضوعًا وغرضًا وحاجة إليه لأن موضوعه كلام الله تعالى الذي هو ينبوع كل حكمة.</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>إذا قرأت ولم تفهم: الناس يتفاوتون في الفهم، والتفسير هو العلم الذي يُفهم به القرآن وتُبيَّن معانيه.</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>أقرأ القرآن وما أفهم، شو أسوي؟ | ما هو التفسير؟ | كيف أفهم الكلمات الصعبة في القرآن؟ | هل أحتاج تفسير لأفهم القرآن؟</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P19" s="6" t="n"/>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>ثلاث فقرات من الفصل: المدخل، وتعريف الزركشي (حذفت تعريف أبي حيان المطوّل)، وأول جملة من «شرف التفسير». لا يرشح المصدر تفسيراً بعينه للمبتدئ؛ يبقى ق-18 في «الناقص».</t>
         </is>
       </c>
       <c r="R19" s="6" t="n"/>
@@ -2082,49 +2348,99 @@
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
     </row>
-    <row r="20" ht="48" customHeight="1">
+    <row r="20" ht="150" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>قالب</t>
+          <t>مقطع</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ست-02</t>
+          <t>ق-20</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>التباس بين ح2 وح7</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>أساسي</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>م-03</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>مباحث في علوم القرآن، مناع القطان — الفصل 22: ترجمة القرآن — معنى الترجمة، وحكم الترجمة الحرفية، والترجمة التفسيرية (ص 324–327 حسب فهرس الكتاب) — https://quranpedia.net/book/23563</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>ترجمة القرآن: هل الترجمة قرآن؟</t>
+        </is>
+      </c>
       <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>هل ترجمة القرآن تعتبر قرآناً؟ | ما الفرق بين القرآن وترجمته؟ | هل يجوز ترجمة القرآن؟</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>هل تقصد كيف كان الوحي يأتي النبي ﷺ، أم لماذا يؤمن المسلمون أن القرآن من عند الله؟</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n"/>
-      <c r="N20" s="6" t="n"/>
+          <t>والترجمة تطلق على معنيين:
+أولهما: الترجمة الحرفية: وهي نقل ألفاظ من لغة إلى نظائرها من اللغة الأخرى بحيث يكون النظم موافقًا للنظم، والترتيب موافقًا للترتيب.
+ثانيهما: الترجمة التفسيرية أو المعنوية: وهي بيان معنى الكلام بلغة أخرى من غير تقييد بترتيب كلمات الأصل أو مراعاة لنظمه.
+[…]
+ولا يقول أحد من الناس إن الكلمة من القرآن إذا ترجمت يقال فيها إنها كلام الله، فإن الله لم يتكلم إلا بما تتلوه بالعربية […]
+ويحق لنا أن نقول: إن علماء الإسلام إذا قاموا بتفسير للقرآن، يتوخى فيه أداء المعنى القريب الميسور الراجح، ثم يترجم هذا التفسير بأمانة وبراعة، فإن هذا يقال فيه: "ترجمة تفسير القرآن" أو "ترجمة تفسيرية" بمعنى شرح الكلام وبيان معناه بلغة أخرى. ولا بأس بذلك. […]
+فالمفسِّر يقول في تفسير الآية: يعني كذا، ويذكر فهمه الخاص. والمترجم يقول: معنى هذا الكلام هو عين معنى الآية، وقد عرفنا ما في ذلك.</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>الترجمة ليست قرآناً؛ القرآن هو النص العربي، وما يُترجم هو تفسير لمعانيه بلغة أخرى.</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>هل الترجمة تعتبر قرآناً؟ | أقدر أقرأ القرآن بالإنجليزي؟ | ما الفرق بين القرآن وترجمة معانيه؟ | ليش يقولون ترجمة معاني القرآن؟</t>
+        </is>
+      </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>أ</t>
+        </is>
+      </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
           <t>لا</t>
         </is>
       </c>
-      <c r="P20" s="6" t="n"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="n"/>
+          <t>القصوص «[…]»: شرح اختلاف تراكيب اللغات، وبقية حكم الترجمة الحرفية (فيه لفظ «حرمة»)، والحديث وما بعده. «القراءة في الصلاة بغير العربية» خارج النطاق (فتوى) ولم تؤخذ.</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>المقطع يقتصر على أن الترجمة ليست قرآناً وأن ترجمة التفسير لا بأس بها، ولم أنقل لفظ الحكم «حرمة». هل يكفي هذا؟</t>
+        </is>
+      </c>
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
@@ -2138,12 +2454,12 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ست-03</t>
+          <t>و-01</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>سؤال عن «نسخ مختلفة» أو تغيّر القرآن</t>
+          <t>أعلى كل صفحة</t>
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
@@ -2155,7 +2471,7 @@
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>هل تسأل: هل القرآن الذي بين أيدينا هو نفسه الذي نزل على النبي ﷺ؟</t>
+          <t>«دليل» أداة تستعين بالذكاء الاصطناعي لتختار لك مقطعاً من مصادر إسلامية معتمدة راجعها مختص. لا تكتب إجابات من عندها، وقد تخطئ في الاختيار.</t>
         </is>
       </c>
       <c r="L21" s="6" t="n"/>
@@ -2186,12 +2502,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ست-04</t>
+          <t>و-02</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>سؤال واسع</t>
+          <t>بعد كل جزء معروض</t>
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
@@ -2203,7 +2519,7 @@
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>يمكننا أن نبدأ من أكثر من جهة، فبأيّها تبدأ؟</t>
+          <t>هل أجاب هذا عن سؤالك؟  [نعم] [جزئياً] [لا]</t>
         </is>
       </c>
       <c r="L22" s="6" t="n"/>
@@ -2234,12 +2550,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ام-01</t>
+          <t>و-03</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>سؤال خارج القرآن</t>
+          <t>بعد «جزئياً»</t>
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
@@ -2251,7 +2567,7 @@
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>يختص «دليل» حالياً بالتعرّف إلى القرآن الكريم، وسؤالك عن موضوع آخر. يمكنك الرجوع إلى الموسوعات العلمية في موقع الدرر السنية (dorar.net).</t>
+          <t>ما الذي بقي دون إجابة؟ اكتبه بكلماتك.</t>
         </is>
       </c>
       <c r="L23" s="6" t="n"/>
@@ -2265,7 +2581,7 @@
       <c r="P23" s="6" t="n"/>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>مراجعة شرعية: لا</t>
         </is>
       </c>
       <c r="R23" s="6" t="n"/>
@@ -2282,12 +2598,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ام-02</t>
+          <t>و-04</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>فتوى أو حالة شخصية (المستوى د)</t>
+          <t>فوق كل مقطع (يُملأ من السجل)</t>
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
@@ -2299,7 +2615,7 @@
       <c r="J24" s="6" t="n"/>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>سؤالك يحتاج إلى جواب يراعي حالتك بعينها، وهذا خارج ما يقدمه «دليل». ننصحك بسؤال عالم أو جهة إفتاء موثوقة في بلدك.</t>
+          <t>يجيب هذا المقطع عن: {يجيب_عن}</t>
         </is>
       </c>
       <c r="L24" s="6" t="n"/>
@@ -2313,7 +2629,7 @@
       <c r="P24" s="6" t="n"/>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>مراجعة شرعية: لا</t>
         </is>
       </c>
       <c r="R24" s="6" t="n"/>
@@ -2330,12 +2646,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>ام-03</t>
+          <t>و-05</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>القراءات وأوجه الأداء (قرار نطاق)</t>
+          <t>تحت وصف «يجيب عن»</t>
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
@@ -2347,7 +2663,7 @@
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>تفاصيل القراءات علم متخصص لا يغطيه «دليل» في نسخته الحالية، ويُرجع فيه إلى أهل الاختصاص.</t>
+          <t>وصف مساعد كُتب بمساعدة الذكاء الاصطناعي وراجعه صاحب المشروع. النص المعتمد هو المقتبس.</t>
         </is>
       </c>
       <c r="L25" s="6" t="n"/>
@@ -2361,7 +2677,7 @@
       <c r="P25" s="6" t="n"/>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>مراجعة شرعية: لا</t>
         </is>
       </c>
       <c r="R25" s="6" t="n"/>
@@ -2378,12 +2694,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>ام-04</t>
+          <t>ست-01</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>«الإعجاز العلمي» (قرار نطاق)</t>
+          <t>التباس بين ح1 وح7</t>
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
@@ -2395,7 +2711,7 @@
       <c r="J26" s="6" t="n"/>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>هذا الموضوع خارج ما تغطيه هذه النسخة من «دليل».</t>
+          <t>هل تريد تعريفاً بالقرآن ومكانته، أم الأسباب التي تجعل المسلمين يؤمنون أنه من عند الله؟</t>
         </is>
       </c>
       <c r="L26" s="6" t="n"/>
@@ -2426,12 +2742,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>ام-05</t>
+          <t>ست-02</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>طلب حديث أو نص غير موجود في المواد</t>
+          <t>التباس بين ح2 وح7</t>
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
@@ -2443,7 +2759,7 @@
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>لم نجد في مواد «دليل» المراجعة ما يطابق طلبك، ولا نعرض نصاً لم نتحقق منه. يمكنك البحث في الموسوعة الحديثية بموقع الدرر السنية، مع حكم كل حديث.</t>
+          <t>هل تقصد كيف كان الوحي يأتي النبي ﷺ، أم لماذا يؤمن المسلمون أن القرآن من عند الله؟</t>
         </is>
       </c>
       <c r="L27" s="6" t="n"/>
@@ -2474,12 +2790,12 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>ام-06</t>
+          <t>ست-03</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>آية لم تُعثر عليها في المصحف</t>
+          <t>سؤال عن «نسخ مختلفة» أو تغيّر القرآن</t>
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
@@ -2491,7 +2807,7 @@
       <c r="J28" s="6" t="n"/>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>لم نجد آية تطابق النص الذي كتبته. يمكنك البحث عنها في مصحف موثوق مثل quranpedia.net.</t>
+          <t>هل تسأل: هل القرآن الذي بين أيدينا هو نفسه الذي نزل على النبي ﷺ؟</t>
         </is>
       </c>
       <c r="L28" s="6" t="n"/>
@@ -2505,7 +2821,7 @@
       <c r="P28" s="6" t="n"/>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R28" s="6" t="n"/>
@@ -2522,12 +2838,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>ام-07</t>
+          <t>ست-04</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>الحاجة داخل النطاق ولا جزء مناسب</t>
+          <t>سؤال واسع</t>
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
@@ -2539,7 +2855,7 @@
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>لم نجد في مواد «دليل» المراجعة جزءاً يجيب عن هذا بدقة. نفضّل أن نخبرك بذلك على أن نعرض عليك ما لا يجيب. اختر من الأسئلة المتاحة أدناه.</t>
+          <t>يمكننا أن نبدأ من أكثر من جهة، فبأيّها تبدأ؟</t>
         </is>
       </c>
       <c r="L29" s="6" t="n"/>
@@ -2570,12 +2886,12 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>ام-08</t>
+          <t>ام-01</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>سؤال بغير العربية</t>
+          <t>سؤال خارج القرآن</t>
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
@@ -2587,7 +2903,7 @@
       <c r="J30" s="6" t="n"/>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>يعمل «دليل» حالياً باللغة العربية فقط. — Daleel currently works in Arabic only.</t>
+          <t>يختص «دليل» حالياً بالتعرّف إلى القرآن الكريم، وسؤالك عن موضوع آخر. يمكنك الرجوع إلى الموسوعات العلمية في موقع الدرر السنية (dorar.net).</t>
         </is>
       </c>
       <c r="L30" s="6" t="n"/>
@@ -2601,7 +2917,7 @@
       <c r="P30" s="6" t="n"/>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R30" s="6" t="n"/>
@@ -2618,12 +2934,12 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>ام-09</t>
+          <t>ام-02</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>تفسير آية بعينها (قرار نطاق)</t>
+          <t>فتوى أو حالة شخصية (المستوى د)</t>
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
@@ -2635,7 +2951,7 @@
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>تفسير آيات بعينها خارج ما يغطيه «دليل» حالياً. يمكنك الرجوع إلى موسوعة التفسير بموقع الدرر السنية.</t>
+          <t>سؤالك يحتاج إلى جواب يراعي حالتك بعينها، وهذا خارج ما يقدمه «دليل». ننصحك بسؤال عالم أو جهة إفتاء موثوقة في بلدك.</t>
         </is>
       </c>
       <c r="L31" s="6" t="n"/>
@@ -2666,12 +2982,12 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>ام-10</t>
+          <t>ام-03</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>تعطل خدمة الفهم</t>
+          <t>القراءات وأوجه الأداء (قرار نطاق)</t>
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
@@ -2683,7 +2999,7 @@
       <c r="J32" s="6" t="n"/>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>خدمة فهم الأسئلة متوقفة مؤقتاً. اختر سؤالك من القائمة.</t>
+          <t>تفاصيل القراءات علم متخصص لا يغطيه «دليل» في نسخته الحالية، ويُرجع فيه إلى أهل الاختصاص.</t>
         </is>
       </c>
       <c r="L32" s="6" t="n"/>
@@ -2697,7 +3013,7 @@
       <c r="P32" s="6" t="n"/>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R32" s="6" t="n"/>
@@ -2714,12 +3030,12 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>و-06</t>
+          <t>ام-04</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>فوق نص المقطع (يُملأ من السجل)</t>
+          <t>«الإعجاز العلمي» (قرار نطاق)</t>
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
@@ -2731,7 +3047,7 @@
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>من جواب «{المصدر}» عن سؤال: {عنوان_المسألة}</t>
+          <t>هذا الموضوع خارج ما تغطيه هذه النسخة من «دليل».</t>
         </is>
       </c>
       <c r="L33" s="6" t="n"/>
@@ -2745,7 +3061,7 @@
       <c r="P33" s="6" t="n"/>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R33" s="6" t="n"/>
@@ -2762,12 +3078,12 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>و-07</t>
+          <t>ام-05</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>شاشة البداية</t>
+          <t>طلب حديث أو نص غير موجود في المواد</t>
         </is>
       </c>
       <c r="D34" s="6" t="n"/>
@@ -2779,7 +3095,7 @@
       <c r="J34" s="6" t="n"/>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>اكتب سؤالك عن القرآن بكلماتك، مثل: كيف حُفظ القرآن؟ أو اختر من الأسئلة أدناه.</t>
+          <t>لم نجد في مواد «دليل» المراجعة ما يطابق طلبك، ولا نعرض نصاً لم نتحقق منه. يمكنك البحث في الموسوعة الحديثية بموقع الدرر السنية، مع حكم كل حديث.</t>
         </is>
       </c>
       <c r="L34" s="6" t="n"/>
@@ -2793,7 +3109,7 @@
       <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R34" s="6" t="n"/>
@@ -2810,12 +3126,12 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>و-08</t>
+          <t>ام-06</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>سطر الخصوصية</t>
+          <t>آية لم تُعثر عليها في المصحف</t>
         </is>
       </c>
       <c r="D35" s="6" t="n"/>
@@ -2827,7 +3143,7 @@
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>لا تكتب اسمك أو أي معلومات شخصية. لا نحفظ نص سؤالك، ونرسله إلى مزوّد النموذج اللغوي لفهمه فقط.</t>
+          <t>لم نجد آية تطابق النص الذي كتبته. يمكنك البحث عنها في مصحف موثوق مثل quranpedia.net.</t>
         </is>
       </c>
       <c r="L35" s="6" t="n"/>
@@ -2858,12 +3174,12 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>و-09</t>
+          <t>ام-07</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>بعد «لا»</t>
+          <t>الحاجة داخل النطاق ولا جزء مناسب</t>
         </is>
       </c>
       <c r="D36" s="6" t="n"/>
@@ -2875,7 +3191,7 @@
       <c r="J36" s="6" t="n"/>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>شكراً لإخبارنا. يمكنك إعادة صياغة سؤالك، أو اختيار سؤال من القائمة.</t>
+          <t>لم نجد في مواد «دليل» المراجعة جزءاً يجيب عن هذا بدقة. نفضّل أن نخبرك بذلك على أن نعرض عليك ما لا يجيب. اختر من الأسئلة المتاحة أدناه.</t>
         </is>
       </c>
       <c r="L36" s="6" t="n"/>
@@ -2906,12 +3222,12 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>و-10</t>
+          <t>ام-08</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>بعد «نعم»</t>
+          <t>سؤال بغير العربية</t>
         </is>
       </c>
       <c r="D37" s="6" t="n"/>
@@ -2923,7 +3239,7 @@
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>قد يهمك بعدها:</t>
+          <t>يعمل «دليل» حالياً باللغة العربية فقط. — Daleel currently works in Arabic only.</t>
         </is>
       </c>
       <c r="L37" s="6" t="n"/>
@@ -2954,12 +3270,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>و-11</t>
+          <t>ام-09</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>إدخال فارغ أو غير مفهوم</t>
+          <t>تفسير آية بعينها (قرار نطاق)</t>
         </is>
       </c>
       <c r="D38" s="6" t="n"/>
@@ -2971,7 +3287,7 @@
       <c r="J38" s="6" t="n"/>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>لم نتمكن من قراءة سؤالك. اكتب سؤالاً قصيراً عن القرآن، أو اختر من القائمة.</t>
+          <t>تفسير آيات بعينها خارج ما يغطيه «دليل» حالياً. يمكنك الرجوع إلى موسوعة التفسير بموقع الدرر السنية.</t>
         </is>
       </c>
       <c r="L38" s="6" t="n"/>
@@ -2985,7 +3301,7 @@
       <c r="P38" s="6" t="n"/>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: لا</t>
+          <t>مراجعة شرعية: نعم</t>
         </is>
       </c>
       <c r="R38" s="6" t="n"/>
@@ -3002,12 +3318,12 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>و-12</t>
+          <t>ام-10</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>ما بقي غير مغطى</t>
+          <t>تعطل خدمة الفهم</t>
         </is>
       </c>
       <c r="D39" s="6" t="n"/>
@@ -3019,7 +3335,7 @@
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>لم نجد في مواد «دليل» جزءاً آخر يجيب عمّا بقي من سؤالك. نفضّل أن نخبرك بذلك على أن نعرض ما لا يجيب.</t>
+          <t>خدمة فهم الأسئلة متوقفة مؤقتاً. اختر سؤالك من القائمة.</t>
         </is>
       </c>
       <c r="L39" s="6" t="n"/>
@@ -3050,12 +3366,12 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>و-13</t>
+          <t>و-06</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>آية مطابقة للمصحف</t>
+          <t>فوق نص المقطع (يُملأ من السجل)</t>
         </is>
       </c>
       <c r="D40" s="6" t="n"/>
@@ -3067,7 +3383,7 @@
       <c r="J40" s="6" t="n"/>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>هذا نص الآية كما في المصحف:</t>
+          <t>من جواب «{المصدر}» عن سؤال: {عنوان_المسألة}</t>
         </is>
       </c>
       <c r="L40" s="6" t="n"/>
@@ -3098,12 +3414,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>و-14</t>
+          <t>و-07</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>آية مكتوبة بنص مختلف</t>
+          <t>شاشة البداية</t>
         </is>
       </c>
       <c r="D41" s="6" t="n"/>
@@ -3115,7 +3431,7 @@
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>النص الذي كتبته يختلف عن نص المصحف. هذا نص الآية كما في المصحف:</t>
+          <t>اكتب سؤالك عن القرآن بكلماتك، مثل: كيف حُفظ القرآن؟ أو اختر من الأسئلة أدناه.</t>
         </is>
       </c>
       <c r="L41" s="6" t="n"/>
@@ -3129,7 +3445,7 @@
       <c r="P41" s="6" t="n"/>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>مراجعة شرعية: نعم</t>
+          <t>مراجعة شرعية: لا</t>
         </is>
       </c>
       <c r="R41" s="6" t="n"/>
@@ -3146,12 +3462,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>و-15</t>
+          <t>و-08</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>أسفل كل مقطع</t>
+          <t>سطر الخصوصية</t>
         </is>
       </c>
       <c r="D42" s="6" t="n"/>
@@ -3163,7 +3479,7 @@
       <c r="J42" s="6" t="n"/>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>لا يتجاوز «دليل» هذا النص المقتبس، ولا يضيف إليه شرحاً من عنده.</t>
+          <t>لا تكتب اسمك أو أي معلومات شخصية. لا نحفظ نص سؤالك، ونرسله إلى مزوّد النموذج اللغوي لفهمه فقط.</t>
         </is>
       </c>
       <c r="L42" s="6" t="n"/>
@@ -3186,14 +3502,359 @@
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
     </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>و-09</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>بعد «لا»</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>شكراً لإخبارنا. يمكنك إعادة صياغة سؤالك، أو اختيار سؤال من القائمة.</t>
+        </is>
+      </c>
+      <c r="L43" s="6" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="6" t="n"/>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="n"/>
+      <c r="S43" s="8" t="n"/>
+      <c r="T43" s="8" t="n"/>
+      <c r="U43" s="8" t="n"/>
+      <c r="V43" s="8" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>و-10</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>بعد «نعم»</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n"/>
+      <c r="H44" s="6" t="n"/>
+      <c r="I44" s="6" t="n"/>
+      <c r="J44" s="6" t="n"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>قد يهمك بعدها:</t>
+        </is>
+      </c>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="n"/>
+      <c r="N44" s="6" t="n"/>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="n"/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="n"/>
+      <c r="S44" s="8" t="n"/>
+      <c r="T44" s="8" t="n"/>
+      <c r="U44" s="8" t="n"/>
+      <c r="V44" s="8" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>و-11</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>إدخال فارغ أو غير مفهوم</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="n"/>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>لم نتمكن من قراءة سؤالك. اكتب سؤالاً قصيراً عن القرآن، أو اختر من القائمة.</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="6" t="n"/>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="n"/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="n"/>
+      <c r="S45" s="8" t="n"/>
+      <c r="T45" s="8" t="n"/>
+      <c r="U45" s="8" t="n"/>
+      <c r="V45" s="8" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>و-12</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>ما بقي غير مغطى</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>لم نجد في مواد «دليل» جزءاً آخر يجيب عمّا بقي من سؤالك. نفضّل أن نخبرك بذلك على أن نعرض ما لا يجيب.</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="n"/>
+      <c r="N46" s="6" t="n"/>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="n"/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="n"/>
+      <c r="S46" s="8" t="n"/>
+      <c r="T46" s="8" t="n"/>
+      <c r="U46" s="8" t="n"/>
+      <c r="V46" s="8" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>و-13</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>آية مطابقة للمصحف</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="n"/>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>هذا نص الآية كما في المصحف:</t>
+        </is>
+      </c>
+      <c r="L47" s="6" t="n"/>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="6" t="n"/>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="n"/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="n"/>
+      <c r="S47" s="8" t="n"/>
+      <c r="T47" s="8" t="n"/>
+      <c r="U47" s="8" t="n"/>
+      <c r="V47" s="8" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>و-14</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>آية مكتوبة بنص مختلف</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="6" t="n"/>
+      <c r="I48" s="6" t="n"/>
+      <c r="J48" s="6" t="n"/>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>النص الذي كتبته يختلف عن نص المصحف. هذا نص الآية كما في المصحف:</t>
+        </is>
+      </c>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="n"/>
+      <c r="N48" s="6" t="n"/>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="n"/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: نعم</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="n"/>
+      <c r="S48" s="8" t="n"/>
+      <c r="T48" s="8" t="n"/>
+      <c r="U48" s="8" t="n"/>
+      <c r="V48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>و-15</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>أسفل كل مقطع</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>لا يتجاوز «دليل» هذا النص المقتبس، ولا يضيف إليه شرحاً من عنده.</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="6" t="n"/>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="n"/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>مراجعة شرعية: لا</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="n"/>
+      <c r="S49" s="8" t="n"/>
+      <c r="T49" s="8" t="n"/>
+      <c r="U49" s="8" t="n"/>
+      <c r="V49" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V42"/>
+  <autoFilter ref="A1:V49"/>
   <conditionalFormatting sqref="O2:O300">
     <cfRule type="expression" priority="1" dxfId="1">
       <formula>$O2="نعم"</formula>
     </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>$O2="نعم"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"موافق,موافق بتعديل,غير موافق"</formula1>
+    </dataValidation>
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
     </dataValidation>
@@ -4875,7 +5536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4921,255 +5582,39 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>ق-05</t>
+          <t>ق-18</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>ح5</t>
+          <t>ح6</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>أساسي</t>
+          <t>إضافي</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>التوحيد وعبادة الله: الرسالة المحورية للقرآن</t>
+          <t>من أين يبدأ المبتدئ القراءة</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>كتاب في علوم القرآن (quranpedia) أو الدرر — يُحدد</t>
+          <t>لم يُعثر عليه في كتاب القطان؛ يُبحث في الدرر أو بينات</t>
         </is>
       </c>
       <c r="F2" s="6" t="n"/>
     </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ق-06</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>ح5</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>الأنبياء وقصصهم في القرآن</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>كتاب في علوم القرآن (quranpedia) أو الدرر — يُحدد</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ق-07</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>ح5</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>اليوم الآخر والقيم في القرآن إجمالاً</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>كتاب في علوم القرآن (quranpedia) أو الدرر — يُحدد</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>ق-10</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>ح2</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>المكي والمدني</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>كتاب في علوم القرآن (quranpedia) — يُحدد</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>ق-15</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>السورة والآية، وعدد سور القرآن</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>كتاب في علوم القرآن (quranpedia) — يُحدد</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>ق-16</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>كيف أصل إلى سورة وآية في المصحف</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>كتاب في علوم القرآن (quranpedia) — يُحدد</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>ق-19</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>فهم المعنى بتفسير مختصر موثوق</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>الدرر أو كتاب في علوم القرآن — يُحدد</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>ق-20</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>أساسي</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>الفرق بين نص القرآن وتفسيره وترجمة معانيه</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>الدرر أو كتاب في علوم القرآن — يُحدد</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>ق-18</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>إضافي</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>من أين يبدأ المبتدئ القراءة</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>الدرر أو كتاب في علوم القرآن — يُحدد</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-    </row>
+    <row r="3" ht="34" customHeight="1"/>
+    <row r="4" ht="34" customHeight="1"/>
+    <row r="5" ht="34" customHeight="1"/>
+    <row r="6" ht="34" customHeight="1"/>
+    <row r="7" ht="34" customHeight="1"/>
+    <row r="8" ht="34" customHeight="1"/>
+    <row r="9" ht="34" customHeight="1"/>
+    <row r="10" ht="34" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5241,7 +5686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5372,7 +5817,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>[كتاب مختصر في علوم القرآن — يُحدد]</t>
+          <t>مباحث في علوم القرآن، مناع القطان</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -5382,7 +5827,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>[الرابط]</t>
+          <t>https://quranpedia.net/book/23563</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -5390,65 +5835,73 @@
           <t>معروضة</t>
         </is>
       </c>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>ح2 ح4</t>
+          <t>ح2 ح4 ح5 ح6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>م-04</t>
+          <t>ت-01</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>[مادة للبدء بالقراءة والفهم — يُحدد]</t>
+          <t>مصحف مجمع الملك فهد (نص الآيات)</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>الدرر أو الجمهرة</t>
+          <t>مجمع الملك فهد</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>[الرابط]</t>
+          <t>https://quranpedia.net</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>معروضة</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
+          <t>تحقق فقط</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>ح5 ح6</t>
+          <t>كل الحاجات</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>ت-01</t>
+          <t>ت-02</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>مصحف مجمع الملك فهد (نص الآيات)</t>
+          <t>الموسوعة الحديثية</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>مجمع الملك فهد</t>
+          <t>الدرر السنية</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>https://quranpedia.net</t>
+          <t>https://dorar.net/hadith</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -5462,43 +5915,6 @@
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>كل الحاجات</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>ت-02</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>الموسوعة الحديثية</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>الدرر السنية</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>https://dorar.net/hadith</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>تحقق فقط</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>كل الحاجات</t>
         </is>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -660,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,7 @@
     <col width="36" customWidth="1" min="20" max="20"/>
     <col width="18" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -796,6 +797,11 @@
       <c r="V1" s="4" t="inlineStr">
         <is>
           <t>رأي المختص الأعلم</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>لا يُجتزأ</t>
         </is>
       </c>
     </row>
@@ -2255,6 +2261,11 @@
       <c r="T18" s="8" t="n"/>
       <c r="U18" s="8" t="n"/>
       <c r="V18" s="8" t="n"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -3837,6 +3848,51 @@
       <c r="T49" s="8" t="n"/>
       <c r="U49" s="8" t="n"/>
       <c r="V49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>ام-11</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>زر تحت الامتناع عن تفسير آية بعينها، أو تحت آية كتبها المستخدم</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="6" t="n"/>
+      <c r="I50" s="6" t="n"/>
+      <c r="J50" s="6" t="n"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>اقرأ معنى {الموضع} في «التفسير الميسر» (مجمع الملك فهد) على منصة القرآن الكريم</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="n"/>
+      <c r="M50" s="6" t="n"/>
+      <c r="N50" s="6" t="n"/>
+      <c r="O50" s="6" t="n"/>
+      <c r="P50" s="6" t="n"/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>يُحيل إلى صفحة التفسير الميسر للآية على quran.com ولا يعرض تفسيراً داخل «دليل». مراجعة شرعية: نعم (اختيار التفسير المُحال إليه).</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="n"/>
+      <c r="S50" s="6" t="n"/>
+      <c r="T50" s="6" t="n"/>
+      <c r="U50" s="6" t="n"/>
+      <c r="V50" s="6" t="n"/>
+      <c r="W50" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V49"/>
@@ -3848,7 +3904,7 @@
       <formula>$O2="نعم"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
     </dataValidation>
@@ -3861,6 +3917,9 @@
     <dataValidation sqref="V2:V300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"موافق,موافق بتعديل,غير موافق"</formula1>
     </dataValidation>
+    <dataValidation sqref="W2:W300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"نعم,لا"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3872,7 +3931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3894,6 +3953,7 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -3990,6 +4050,11 @@
       <c r="S1" s="4" t="inlineStr">
         <is>
           <t>صالح للنشر</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>لا يُجتزأ</t>
         </is>
       </c>
     </row>
@@ -5467,6 +5532,11 @@
       <formula>$N2="نعم"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="T2:T300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"نعم,لا"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -227,6 +227,21 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>دليل</author>
+  </authors>
+  <commentList>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>اختياري: رقم المقطع (أو أكثر، مثل ق-01 ق-02) الذي يُعرض عند الضغط على زر هذه الحاجة. إن تُرك فارغاً يُعرض أول مقطع «أساسي» منشور، ويختفي الزر إن لم يوجد.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -660,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3893,6 +3908,51 @@
       <c r="U50" s="6" t="n"/>
       <c r="V50" s="6" t="n"/>
       <c r="W50" s="6" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>ام-12</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>سؤال لا علاقة له بالدين (طبخ، رياضة، معلومات عامة)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="n"/>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>«دليل» مختص بالأسئلة عن القرآن الكريم، وسؤالك خارج هذا المجال. جرّب أن تسأل عن القرآن، أو اختر من الأسئلة أدناه.</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="6" t="n"/>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="6" t="n"/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>بديل عن ام-01 للأسئلة غير الدينية، حتى لا يُحال سؤال الطبخ إلى مرجع شرعي. مراجعة شرعية: لا.</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="n"/>
+      <c r="S51" s="6" t="n"/>
+      <c r="T51" s="6" t="n"/>
+      <c r="U51" s="6" t="n"/>
+      <c r="V51" s="6" t="n"/>
+      <c r="W51" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V49"/>
@@ -6001,7 +6061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6013,6 +6073,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6061,6 +6122,11 @@
           <t>التغطية</t>
         </is>
       </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>مقطع الزر</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
@@ -6105,6 +6171,7 @@
         <f>IF(H2=0,"لا تغطية",IF(H2&lt;G2,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J2" s="7" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -6149,6 +6216,7 @@
         <f>IF(H3=0,"لا تغطية",IF(H3&lt;G3,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -6193,6 +6261,7 @@
         <f>IF(H4=0,"لا تغطية",IF(H4&lt;G4,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -6237,6 +6306,7 @@
         <f>IF(H5=0,"لا تغطية",IF(H5&lt;G5,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -6281,6 +6351,7 @@
         <f>IF(H6=0,"لا تغطية",IF(H6&lt;G6,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -6325,6 +6396,7 @@
         <f>IF(H7=0,"لا تغطية",IF(H7&lt;G7,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -6369,9 +6441,11 @@
         <f>IF(H8=0,"لا تغطية",IF(H8&lt;G8,"جزئية","مكتملة"))</f>
         <v/>
       </c>
+      <c r="J8" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -230,6 +230,36 @@
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>دليل</author>
+  </authors>
+  <commentList>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>أسئلة قريبة من موضوع المقطع لا يجيب عنها، تفصل بينها «|». يراها الموجِّه فلا يختار المقطع لها، وتُبنى منها حالات اختبار. مسودة بمساعدة الذكاء الاصطناعي.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>دليل</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>أسئلة قريبة من موضوع المقطع لا يجيب عنها، تفصل بينها «|». يراها الموجِّه فلا يختار المقطع لها، وتُبنى منها حالات اختبار. مسودة بمساعدة الذكاء الاصطناعي.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>دليل</author>
@@ -675,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -701,6 +731,7 @@
     <col width="18" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -817,6 +848,11 @@
       <c r="W1" s="4" t="inlineStr">
         <is>
           <t>لا يُجتزأ</t>
+        </is>
+      </c>
+      <c r="X1" s="4" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
         </is>
       </c>
     </row>
@@ -899,6 +935,11 @@
       <c r="T2" s="8" t="n"/>
       <c r="U2" s="8" t="n"/>
       <c r="V2" s="8" t="n"/>
+      <c r="X2" s="8" t="inlineStr">
+        <is>
+          <t>لماذا يعظّم المسلمون القرآن؟ | هل القرآن من تأليف محمد؟ | ما معنى كلمة قرآن في اللغة؟</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -982,6 +1023,11 @@
       <c r="T3" s="8" t="n"/>
       <c r="U3" s="8" t="n"/>
       <c r="V3" s="8" t="n"/>
+      <c r="X3" s="8" t="inlineStr">
+        <is>
+          <t>ما تعريف القرآن؟ | ما فضل قراءة القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -1071,6 +1117,11 @@
       <c r="T4" s="8" t="n"/>
       <c r="U4" s="8" t="n"/>
       <c r="V4" s="8" t="n"/>
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t>هل نقل محمد القرآن من التوراة؟ | ما الفرق بين القرآن والحديث؟</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -1151,6 +1202,11 @@
       <c r="T5" s="8" t="n"/>
       <c r="U5" s="8" t="n"/>
       <c r="V5" s="8" t="n"/>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>ما تعريف القرآن اصطلاحاً؟ | ما أسماء القرآن الأخرى؟</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1234,6 +1290,11 @@
       <c r="T6" s="8" t="n"/>
       <c r="U6" s="8" t="n"/>
       <c r="V6" s="8" t="n"/>
+      <c r="X6" s="8" t="inlineStr">
+        <is>
+          <t>هل السنة حجة؟ | ما تعريف القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1316,6 +1377,11 @@
       <c r="T7" s="8" t="n"/>
       <c r="U7" s="8" t="n"/>
       <c r="V7" s="8" t="n"/>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t>في أي شهر نزل القرآن؟ | لماذا لم ير الناس جبريل؟ | هل نزل القرآن مرة واحدة؟</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1398,6 +1464,11 @@
       <c r="T8" s="8" t="n"/>
       <c r="U8" s="8" t="n"/>
       <c r="V8" s="8" t="n"/>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t>كيف كان الوحي يأتي النبي؟ | هل نزل القرآن مرة واحدة؟ | ما فضل شهر رمضان؟</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
@@ -1478,6 +1549,11 @@
       <c r="T9" s="8" t="n"/>
       <c r="U9" s="8" t="n"/>
       <c r="V9" s="8" t="n"/>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>في أي شهر نزل القرآن؟ | كيف كان الوحي يأتي النبي؟</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1563,6 +1639,11 @@
       <c r="T10" s="8" t="n"/>
       <c r="U10" s="8" t="n"/>
       <c r="V10" s="8" t="n"/>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t>كيف كان الوحي ينزل؟ | من رتّب سور القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
@@ -1650,6 +1731,11 @@
       <c r="T11" s="8" t="n"/>
       <c r="U11" s="8" t="n"/>
       <c r="V11" s="8" t="n"/>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>لماذا جمع عثمان القرآن؟ | كم عدد حفّاظ القرآن اليوم؟</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1732,6 +1818,11 @@
       <c r="T12" s="8" t="n"/>
       <c r="U12" s="8" t="n"/>
       <c r="V12" s="8" t="n"/>
+      <c r="X12" s="8" t="inlineStr">
+        <is>
+          <t>كيف أبدأ قراءة القرآن؟ | ما حكم قراءة القرآن للحائض؟</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
@@ -1814,6 +1905,11 @@
       <c r="T13" s="8" t="n"/>
       <c r="U13" s="8" t="n"/>
       <c r="V13" s="8" t="n"/>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>أين أتعلم القرآن؟ | ما أحكام التجويد؟</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1904,6 +2000,11 @@
       <c r="T14" s="8" t="n"/>
       <c r="U14" s="8" t="n"/>
       <c r="V14" s="8" t="n"/>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t>ما الفرق بين أسلوب السور المكية والمدنية؟ | في أي شهر نزل القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -1994,6 +2095,11 @@
       <c r="T15" s="8" t="n"/>
       <c r="U15" s="8" t="n"/>
       <c r="V15" s="8" t="n"/>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>ما قصة يوسف عليه السلام؟ | ما تفسير سورة الفاتحة؟</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -2088,6 +2194,11 @@
       <c r="T16" s="8" t="n"/>
       <c r="U16" s="8" t="n"/>
       <c r="V16" s="8" t="n"/>
+      <c r="X16" s="8" t="inlineStr">
+        <is>
+          <t>ما قصة نوح بالتفصيل؟ | هل قصص القرآن منقولة من التوراة؟</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -2181,6 +2292,11 @@
       <c r="T17" s="8" t="n"/>
       <c r="U17" s="8" t="n"/>
       <c r="V17" s="8" t="n"/>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t>من رتّب سور القرآن؟ | كيف أجد آية في المصحف؟</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
@@ -2281,6 +2397,11 @@
           <t>نعم</t>
         </is>
       </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t>كم عدد سور القرآن؟ | لماذا تتنقل السورة بين موضوعات مختلفة؟</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
@@ -2373,6 +2494,11 @@
       <c r="T19" s="8" t="n"/>
       <c r="U19" s="8" t="n"/>
       <c r="V19" s="8" t="n"/>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t>ما تفسير آية الكرسي؟ | ما أفضل تفسير للمبتدئ؟</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -2471,6 +2597,11 @@
       <c r="T20" s="8" t="n"/>
       <c r="U20" s="8" t="n"/>
       <c r="V20" s="8" t="n"/>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t>هل تجوز الصلاة بترجمة القرآن؟ | ما أفضل ترجمة للقرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
@@ -3982,6 +4113,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3991,7 +4123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4014,6 +4146,7 @@
     <col width="40" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="34" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -4117,6 +4250,11 @@
           <t>لا يُجتزأ</t>
         </is>
       </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="150" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -4213,6 +4351,11 @@
         <f>IF(A2="","",IF(OR(M2="ج",M2="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D2,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B2="",E2="",J2="",K2="",P2=""),"بيانات ناقصة",IF(AND(N2="نعم",Q2&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>ما علاقة القرآن بالكتب السابقة؟ | ما تعريف القرآن؟ | ما مكانة القرآن عند المسلمين؟</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
@@ -4304,6 +4447,11 @@
       <c r="S3" s="7">
         <f>IF(A3="","",IF(OR(M3="ج",M3="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D3,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B3="",E3="",J3="",K3="",P3=""),"بيانات ناقصة",IF(AND(N3="نعم",Q3&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>كيف نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما معنى سورة مكية؟</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
@@ -4403,6 +4551,11 @@
       <c r="S4" s="7">
         <f>IF(A4="","",IF(OR(M4="ج",M4="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D4,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B4="",E4="",J4="",K4="",P4=""),"بيانات ناقصة",IF(AND(N4="نعم",Q4&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>كيف كان الوحي يأتي النبي؟ | متى بدأ نزول الوحي؟</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
@@ -4500,6 +4653,11 @@
       <c r="S5" s="7">
         <f>IF(A5="","",IF(OR(M5="ج",M5="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D5,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B5="",E5="",J5="",K5="",P5=""),"بيانات ناقصة",IF(AND(N5="نعم",Q5&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>في أي شهر نزل القرآن؟ | هل نزل القرآن مفرقاً؟ | متى جُمع القرآن في مصحف واحد؟</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
@@ -4598,6 +4756,11 @@
       <c r="S6" s="7">
         <f>IF(A6="","",IF(OR(M6="ج",M6="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D6,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B6="",E6="",J6="",K6="",P6=""),"بيانات ناقصة",IF(AND(N6="نعم",Q6&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U6" s="7" t="inlineStr">
+        <is>
+          <t>كيف كان الوحي ينزل على النبي؟ | كم عدد الحفاظ من الصحابة؟</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
@@ -4703,6 +4866,11 @@
         <f>IF(A7="","",IF(OR(M7="ج",M7="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D7,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B7="",E7="",J7="",K7="",P7=""),"بيانات ناقصة",IF(AND(N7="نعم",Q7&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U7" s="7" t="inlineStr">
+        <is>
+          <t>كيف كُتب القرآن زمن النبي؟ | ما القراءات؟</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -4801,6 +4969,11 @@
       <c r="S8" s="7">
         <f>IF(A8="","",IF(OR(M8="ج",M8="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D8,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B8="",E8="",J8="",K8="",P8=""),"بيانات ناقصة",IF(AND(N8="نعم",Q8&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U8" s="7" t="inlineStr">
+        <is>
+          <t>كيف جمع عثمان القرآن؟ | كيف أحفظ القرآن؟</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
@@ -4902,6 +5075,11 @@
         <f>IF(A9="","",IF(OR(M9="ج",M9="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D9,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B9="",E9="",J9="",K9="",P9=""),"بيانات ناقصة",IF(AND(N9="نعم",Q9&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U9" s="7" t="inlineStr">
+        <is>
+          <t>كم عدد سور القرآن؟ | لماذا تتنقل السورة بين موضوعات مختلفة؟</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -4995,6 +5173,11 @@
       <c r="S10" s="7">
         <f>IF(A10="","",IF(OR(M10="ج",M10="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D10,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B10="",E10="",J10="",K10="",P10=""),"بيانات ناقصة",IF(AND(N10="نعم",Q10&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>من رتّب سور القرآن؟ | ما أبرز موضوعات القرآن؟</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
@@ -5091,6 +5274,11 @@
         <f>IF(A11="","",IF(OR(M11="ج",M11="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D11,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B11="",E11="",J11="",K11="",P11=""),"بيانات ناقصة",IF(AND(N11="نعم",Q11&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>ما أفضل ترجمة للقرآن؟ | ما هو التفسير؟ | هل تجوز الصلاة بترجمة القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -5188,6 +5376,11 @@
       <c r="S12" s="7">
         <f>IF(A12="","",IF(OR(M12="ج",M12="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D12,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B12="",E12="",J12="",K12="",P12=""),"بيانات ناقصة",IF(AND(N12="نعم",Q12&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>ما تعريف القرآن؟ | لماذا يعظّم المسلمون القرآن؟ | ما أمثلة الإعجاز العلمي؟</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
@@ -5288,6 +5481,11 @@
         <f>IF(A13="","",IF(OR(M13="ج",M13="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D13,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B13="",E13="",J13="",K13="",P13=""),"بيانات ناقصة",IF(AND(N13="نعم",Q13&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>ما هو القرآن؟ | ما مكانة القرآن؟ | كيف كان الوحي ينزل؟</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -5385,6 +5583,11 @@
         <f>IF(A14="","",IF(OR(M14="ج",M14="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D14,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B14="",E14="",J14="",K14="",P14=""),"بيانات ناقصة",IF(AND(N14="نعم",Q14&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="5" t="inlineStr">
@@ -5481,6 +5684,11 @@
         <f>IF(A15="","",IF(OR(M15="ج",M15="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D15,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B15="",E15="",J15="",K15="",P15=""),"بيانات ناقصة",IF(AND(N15="نعم",Q15&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>كيف جُمع القرآن؟ | ما أسباب نزول آية بعينها؟</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
@@ -5578,6 +5786,11 @@
       <c r="S16" s="7">
         <f>IF(A16="","",IF(OR(M16="ج",M16="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D16,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B16="",E16="",J16="",K16="",P16=""),"بيانات ناقصة",IF(AND(N16="نعم",Q16&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>ما أمثلة الإعجاز العلمي؟ | ما مكانة القرآن؟</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5598,6 +5811,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:X52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1108,15 +1108,18 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>يتناول الكتب السابقة (التوراة والإنجيل) ودخول التحريف عليها، وجمهورنا قد يكون غير مسلم.
-1) هل المقطع بحدوده مناسب لسائل غير مسلم يسأل «هل القرآن مثل الإنجيل؟»
-2) هل يُبقى سطر «قد دخله التحريف والتبديل» أم يُقصّ المقطع عند «…وحاكماً عليها كلها»؟</t>
+          <t>توصية اللجنة: يُبقى سطر «قد دخله التحريف والتبديل»، لأن القصّ قبله يحذف القيد ويوهم تصديق الكتب الموجودة الآن مطلقاً، وعُلّم المقطع «لا يُجتزأ» فيُعرض كاملاً. هل يناسب بهذه الحدود سائلاً غير مسلم يسأل «هل القرآن مثل الإنجيل؟»</t>
         </is>
       </c>
       <c r="S4" s="8" t="n"/>
       <c r="T4" s="8" t="n"/>
       <c r="U4" s="8" t="n"/>
       <c r="V4" s="8" t="n"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="X4" s="8" t="inlineStr">
         <is>
           <t>هل نقل محمد القرآن من التوراة؟ | ما الفرق بين القرآن والحديث؟</t>
@@ -1262,7 +1265,7 @@
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
-          <t>ما الفرق بين القرآن والحديث القدسي؟ | هل الحديث القدسي من القرآن؟ | ما الفرق بين القرآن والحديث؟</t>
+          <t>ما الفرق بين القرآن والحديث القدسي؟ | هل الحديث القدسي من القرآن؟ | هل الحديث القدسي كلام الله مثل القرآن؟</t>
         </is>
       </c>
       <c r="N6" s="6" t="inlineStr">
@@ -1285,14 +1288,18 @@
           <t>اخترت الفروق 1–4 من 13؛ تركت 5 و6 و10 و11 لأنها أحكام فقهية (الجنب، الصلاة، التكفير، الاستعاذة)، وتركت 7–9 و12–13 للطول.</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>عبارة «فأغلبه أحاديث آحاد ظني الثبوت» قد يفهمها المبتدئ تشكيكاً في السنة. هل يُبقى البند 2 أم يُقصّ؟</t>
+        </is>
+      </c>
       <c r="S6" s="8" t="n"/>
       <c r="T6" s="8" t="n"/>
       <c r="U6" s="8" t="n"/>
       <c r="V6" s="8" t="n"/>
       <c r="X6" s="8" t="inlineStr">
         <is>
-          <t>هل السنة حجة؟ | ما تعريف القرآن؟</t>
+          <t>هل السنة حجة؟ | ما تعريف القرآن؟ | ما الفرق بين القرآن والحديث؟</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1785,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>عن أبي هُرَيرةَ رَضِيَ اللهُ عنه أنَّ رَسولَ اللهِ صلَّى اللهُ عليه وسلَّم قال: ((وما اجتمع قومٌ في بيتٍ من بُيوتِ اللهِ يَتْلون كِتابَ اللهِ ويتدارسونَه بينهم، إلَّا نزلت عليهم السَّكينةُ، وغَشِيَتهم الرَّحمةُ، وحَفَّتْهم المَلائِكةُ، وذكرهم اللهُ فيمَن عِندَه )) .
+          <t>عن أبي هُرَيرةَ رَضِيَ اللهُ عنه أنَّ رَسولَ اللهِ صلَّى اللهُ عليه وسلَّم قال: ((… وما اجتمع قومٌ في بيتٍ من بُيوتِ اللهِ يَتْلون كِتابَ اللهِ ويتدارسونَه بينهم، إلَّا نزلت عليهم السَّكينةُ، وغَشِيَتهم الرَّحمةُ، وحَفَّتْهم المَلائِكةُ، وذكرهم اللهُ فيمَن عِندَه )) .
 […]
 قال ابنُ عُثَيمين: (هذا القُرْآنُ له فضائلُ عظيمةٌ؛ فضائِلُ عامَّةٌ، وفضائِلُ في آياتٍ وسُوَرٍ خاصَّةٍ؛ مثلًا الفاتحةُ هي السَّبعُ المثاني وهي أمُّ الكِتابِ، آيةُ الكرسيِّ هي أعظَمُ آيةٍ في كِتابِ الله، وهَلُمَّ جَرًّا، هناك آياتٌ أو سُوَرٌ لها فضلٌ خاصٌّ، أمَّا القُرْآنُ عمومًا فله أيضًا فضائِلُ عامَّةٌ، وهذا يوجِبُ علينا أن نحرِصَ غايةَ الحِرصِ على تلاوةِ كِتابِ اللهِ عَزَّ وجَلَّ ليلًا ونهارًا) .</t>
         </is>
@@ -1810,7 +1817,7 @@
       </c>
       <c r="Q12" s="6" t="inlineStr">
         <is>
-          <t>قصّ «[…]»: حذفت شرح المنح الأربع للطول، وأبقيت الحديث وكلام ابن عثيمين. يجيب عن «لماذا أقرأ» لا عن «من أين أبدأ».</t>
+          <t>قصّ «[…]»: حذفت شرح المنح الأربع للطول، وأبقيت الحديث وكلام ابن عثيمين. يجيب عن «لماذا أقرأ» لا عن «من أين أبدأ». [5 أكتوبر] الحديث مقطوع من أوله في المصدر، فوُضعت علامة البتر. التخريج: صحيح مسلم (2699)، يُتحقق منه.</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr"/>
@@ -2056,7 +2063,7 @@
       <c r="K15" s="6" t="inlineStr">
         <is>
           <t>والذي يقرأ القرآن الكريم يجد للآيات المكية خصائص ليست للآيات المدنية في وقعها ومعانيها، وإن كانت الثانية مبنية على الأولى في الأحكام والتشريع.
-[…] نزل الوحي المكي قوارع زاجرة، وشهبًا منذرة، وحججًا قاطعة، يحطم وثنيتهم في العقيدة، ويدعوهم إلى توحيد الألوهية والربوبية، ويهتك أستار فسادهم، ويسَفِّه أحلامهم، ويقيم دلائل النبوة، ويضرب الأمثلة للحياة الآخرة وما فيها من جنة ونار، ويتحداهم -على فصاحتهم- بأن يأتوا بمثل القرآن، ويسوق إليهم قصص المكذبين الغابرين عبرة وذكرى […]
+فحيث كان القوم في جاهلية تعمى وتصم، يعبدون الأوثان، ويشركون بالله، وينكرون الوحي، ويكذبون بيوم الدين […] نزل الوحي المكي قوارع زاجرة، وشهبًا منذرة، وحججًا قاطعة، يحطم وثنيتهم في العقيدة، ويدعوهم إلى توحيد الألوهية والربوبية، ويهتك أستار فسادهم، ويسَفِّه أحلامهم، ويقيم دلائل النبوة، ويضرب الأمثلة للحياة الآخرة وما فيها من جنة ونار، ويتحداهم -على فصاحتهم- بأن يأتوا بمثل القرآن، ويسوق إليهم قصص المكذبين الغابرين عبرة وذكرى […]
 وحين تكونت الجماعة المؤمنة بالله وملائكته وكتبه ورسله واليوم الآخر وبالقدر خيره وشره، وامتُحنت في عقيدتها بأذى المشركين فصبرت وهاجرت بدينها مؤثرة ما عند الله على متع الحياة -حين تكونت هذه الجماعة- نرى الآيات المدنية طويلة المقاطع، تتناول أحكام الإسلام وحدوده، وتدعو إلى الجهاد والاستشهاد في سبيل الله، وتفصل أصول التشريع، وتضع قواعد المجتمع، وتحدد روابط الأسرة، وصلات الأفراد، وعلاقات الدول والأمم، كما تفضح المنافقين وتكشف دخيلتهم، وتجادل أهل الكتاب وتلجم أفواههم -وهذا هو الطابع العام للقرآن المدني.</t>
         </is>
       </c>
@@ -2077,7 +2084,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>لا</t>
+          <t>نعم</t>
         </is>
       </c>
       <c r="P15" s="6" t="inlineStr">
@@ -2087,10 +2094,14 @@
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>قصّان «[…]»: (1) وصف حال المشركين وقولهم مع آيتين، (2) وصف ألفاظ المكي وأساليبه. يغطي هذا المقطع وحده ق-05 وق-07 المخططين (التوحيد، والآخرة، والقيم)، فحذفت ق-07 من «الناقص».</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="n"/>
+          <t>قصّان «[…]»: (1) وصف حال المشركين وقولهم مع آيتين، (2) وصف ألفاظ المكي وأساليبه. يغطي هذا المقطع وحده ق-05 وق-07 المخططين (التوحيد، والآخرة، والقيم)، فحذفت ق-07 من «الناقص». [5 أكتوبر] أُعيدت جملة «فحيث كان القوم…» ليعود إليها الضمير في «وثنيتهم» (ملاحظة اللجنة).</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>فيه «الجهاد والاستشهاد» و«تلجم أفواههم» وصفاً لخطاب القرآن المدني. هل يناسب بحدوده مبتدئاً قد يكون غير مسلم؟</t>
+        </is>
+      </c>
       <c r="S15" s="8" t="n"/>
       <c r="T15" s="8" t="n"/>
       <c r="U15" s="8" t="n"/>
@@ -2156,7 +2167,8 @@
 […]
 النوع الثالث: قصص يتعلق بالحوادث التي وقعت في زمن رسول الله -صلى الله عليه وسلم- كغزوة بدر وأحد في سورة آل عمران، وغزوة حنين وتبوك في التوبة، وغزوة الأحزاب في سورة الأحزاب، والهجرة، والإسراء، ونحو ذلك.
 وللقصص القرآني فوائد نجمل أهمها فيما يأتي:
-1- إيضاح أسس الدعوة إلى الله، وبيان أصول الشرائع التي بعث بها كل نبي: ﴿وَمَا أَرْسَلْنَا مِنْ قَبْلِكَ مِنْ رَسُولٍ إِلَّا نُوحِي إِلَيْهِ أَنَّهُ لَا إِلَهَ إِلَّا أَنَا فَاعْبُدُونِ﴾ [الأنبياء: 25].</t>
+1- إيضاح أسس الدعوة إلى الله، وبيان أصول الشرائع التي بعث بها كل نبي: ﴿وَمَا أَرْسَلْنَا مِنْ قَبْلِكَ مِنْ رَسُولٍ إِلَّا نُوحِي إِلَيْهِ أَنَّهُ لَا إِلَهَ إِلَّا أَنَا فَاعْبُدُونِ﴾ [الأنبياء: 25].
+[…]</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -2186,7 +2198,7 @@
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>قصّ واحد «[…]»: النوع الثاني (فيه عبارة «لم تثبت ثبوتهم» قد تُفهم خطأً، ويحسن عرضها مع شرح). من الفوائد أخذت الأولى فقط لأن البقية لم ترد في النسخة الرقمية.</t>
+          <t>قصّ واحد «[…]»: النوع الثاني (فيه عبارة «لم تثبت ثبوتهم» قد تُفهم خطأً، ويحسن عرضها مع شرح). من الفوائد أخذت الأولى فقط لأن البقية لم ترد في النسخة الرقمية. [5 أكتوبر] أُضيفت علامة القصّ بعد الفائدة الأولى.</t>
         </is>
       </c>
       <c r="R16" s="6" t="n"/>
@@ -2347,7 +2359,7 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>وترتيب الآيات في القرآن الكريم توقيفي عن رسول الله -صلى الله عليه وسلم- وحكى بعضهم الإجماع على ذلك […] فقد كان جبريل يتنزل بالآيات على رسول الله -صلى الله عليه وسلم- ويرشده إلى موضعها من السورة أو الآيات التي نزلت قبل، فيأمر الرسول كتبة الوحي بكتابتها في موضعها ويقول لهم: ضعوا هذه الآيات في السورة التي يُذكر فيها كذا أو كذا، أو ضعوا آية كذا في موضع كذا […]
+          <t>وترتيب الآيات في القرآن الكريم توقيفي عن رسول الله -صلى الله عليه وسلم- وحكى بعضهم الإجماع على ذلك […] فقد كان جبريل يتنزل بالآيات على رسول الله -صلى الله عليه وسلم- ويرشده إلى موضعها من السورة أو الآيات التي نزلت قبل، فيأمر الرسول كتبة الوحي بكتابتها في موضعها […]
 وكان جبريل يعارض رسول الله -صلى الله عليه وسلم- بالقرآن كل عام مرة في رمضان، وعارضه في العام الأخير من حياته مرتين، وكان ذلك العرض على الترتيب المعروف الآن.
 […]
 وبهذا يترجح أن ترتيب السور توقيفي كترتيب الآيات.</t>
@@ -2380,7 +2392,7 @@
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>ثلاثة قصوص «[…]»: أسماء من حكى الإجماع، والأحاديث والآثار (ستحتاج تخريجاً)، ومناقشة الآراء الثلاثة في ترتيب السور. الخلاف في ترتيب السور مذكور في المصدر، والمقطع يعرض الراجح فقط.</t>
+          <t>ثلاثة قصوص «[…]»: أسماء من حكى الإجماع، والأحاديث والآثار (ستحتاج تخريجاً)، ومناقشة الآراء الثلاثة في ترتيب السور. الخلاف في ترتيب السور مذكور في المصدر، والمقطع يعرض الراجح فقط. [5 أكتوبر] قُصّ الأثر «ضعوا هذه الآيات…» لأن في إسناده كلاماً عند المحدّثين (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -2555,7 +2567,7 @@
 […]
 ولا يقول أحد من الناس إن الكلمة من القرآن إذا ترجمت يقال فيها إنها كلام الله، فإن الله لم يتكلم إلا بما تتلوه بالعربية […]
 ويحق لنا أن نقول: إن علماء الإسلام إذا قاموا بتفسير للقرآن، يتوخى فيه أداء المعنى القريب الميسور الراجح، ثم يترجم هذا التفسير بأمانة وبراعة، فإن هذا يقال فيه: "ترجمة تفسير القرآن" أو "ترجمة تفسيرية" بمعنى شرح الكلام وبيان معناه بلغة أخرى. ولا بأس بذلك. […]
-فالمفسِّر يقول في تفسير الآية: يعني كذا، ويذكر فهمه الخاص. والمترجم يقول: معنى هذا الكلام هو عين معنى الآية، وقد عرفنا ما في ذلك.</t>
+فالمفسِّر يقول في تفسير الآية: يعني كذا، ويذكر فهمه الخاص. والمترجم يقول: معنى هذا الكلام هو عين معنى الآية […]</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
@@ -2585,7 +2597,7 @@
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>القصوص «[…]»: شرح اختلاف تراكيب اللغات، وبقية حكم الترجمة الحرفية (فيه لفظ «حرمة»)، والحديث وما بعده. «القراءة في الصلاة بغير العربية» خارج النطاق (فتوى) ولم تؤخذ.</t>
+          <t>القصوص «[…]»: شرح اختلاف تراكيب اللغات، وبقية حكم الترجمة الحرفية (فيه لفظ «حرمة»)، والحديث وما بعده. «القراءة في الصلاة بغير العربية» خارج النطاق (فتوى) ولم تؤخذ. [5 أكتوبر] قُصّ «وقد عرفنا ما في ذلك» لأنها تحيل إلى كلام محذوف.</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -4084,6 +4096,52 @@
       <c r="U51" s="6" t="n"/>
       <c r="V51" s="6" t="n"/>
       <c r="W51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="34" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>ام-13</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>تعطّل خدمة الفهم مع عرض نتيجة بالبحث المباشر</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+      <c r="G52" s="6" t="n"/>
+      <c r="H52" s="6" t="n"/>
+      <c r="I52" s="6" t="n"/>
+      <c r="J52" s="6" t="n"/>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>خدمة فهم الأسئلة متوقفة مؤقتاً، فعرضنا أقرب نص بالبحث المباشر، وقد يكون أقل دقة.</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="n"/>
+      <c r="M52" s="6" t="n"/>
+      <c r="N52" s="6" t="n"/>
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="6" t="n"/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>يحل محل ام-10 حين تُعرض نتيجة، حتى لا يظهر «اختر من القائمة» فوق إجابة (ملاحظة اللجنة). مراجعة شرعية: لا.</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="n"/>
+      <c r="S52" s="6" t="n"/>
+      <c r="T52" s="6" t="n"/>
+      <c r="U52" s="6" t="n"/>
+      <c r="V52" s="6" t="n"/>
+      <c r="W52" s="6" t="n"/>
+      <c r="X52" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V49"/>
@@ -4314,7 +4372,7 @@
       </c>
       <c r="L2" s="6" t="inlineStr">
         <is>
-          <t>هل يكفي القرآن وحده؟ | ما علاقة الحديث بالقرآن؟</t>
+          <t>هل نكتفي بالقرآن عن السنة؟ | لماذا لا يكفي القرآن وحده؟ | هل السنة ضرورية لفهم القرآن؟</t>
         </is>
       </c>
       <c r="M2" s="6" t="inlineStr">
@@ -4344,16 +4402,21 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير. «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S2" s="7">
         <f>IF(A2="","",IF(OR(M2="ج",M2="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D2,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B2="",E2="",J2="",K2="",P2=""),"بيانات ناقصة",IF(AND(N2="نعم",Q2&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="U2" s="7" t="inlineStr">
         <is>
-          <t>ما علاقة القرآن بالكتب السابقة؟ | ما تعريف القرآن؟ | ما مكانة القرآن عند المسلمين؟</t>
+          <t>ما علاقة القرآن بالكتب السابقة؟ | ما تعريف القرآن؟ | ما مكانة القرآن عند المسلمين؟ | ما علاقة الحديث بالقرآن؟ | ما الفرق بين القرآن والحديث؟</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4478,7 @@
       </c>
       <c r="L3" s="6" t="inlineStr">
         <is>
-          <t>ما الفرق بين أسلوب السور المكية والمدنية؟</t>
+          <t>هل القرآن المكي كله شدة والمدني كله لين؟ | لماذا يشتد خطاب القرآن أحياناً ويلين أحياناً؟</t>
         </is>
       </c>
       <c r="M3" s="6" t="inlineStr">
@@ -4441,7 +4504,7 @@
       <c r="Q3" s="6" t="inlineStr"/>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات.</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير.</t>
         </is>
       </c>
       <c r="S3" s="7">
@@ -4450,7 +4513,7 @@
       </c>
       <c r="U3" s="7" t="inlineStr">
         <is>
-          <t>كيف نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما معنى سورة مكية؟</t>
+          <t>كيف نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما معنى سورة مكية؟ | ما الفرق بين أسلوب السور المكية والمدنية؟</t>
         </is>
       </c>
     </row>
@@ -4545,12 +4608,17 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S4" s="7">
         <f>IF(A4="","",IF(OR(M4="ج",M4="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D4,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B4="",E4="",J4="",K4="",P4=""),"بيانات ناقصة",IF(AND(N4="نعم",Q4&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
       </c>
       <c r="U4" s="7" t="inlineStr">
         <is>
@@ -4621,7 +4689,7 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>كيف حُفظ القرآن زمن النبي؟ | هل كان الصحابة يحفظون القرآن؟ | من كان يكتب الوحي؟</t>
+          <t>كيف حُفظ القرآن زمن النبي؟ | هل كان الصحابة يحفظون القرآن؟ | كيف دُوّن القرآن في حياة النبي؟</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr">
@@ -4647,7 +4715,7 @@
       <c r="Q5" s="6" t="inlineStr"/>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات.</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير. للمراجعة: «مرتباً كما هو الآن» هنا، وق-17 يذكر الخلاف في ترتيب السور؛ هل يحتاج توضيحاً؟</t>
         </is>
       </c>
       <c r="S5" s="7">
@@ -4656,7 +4724,7 @@
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>في أي شهر نزل القرآن؟ | هل نزل القرآن مفرقاً؟ | متى جُمع القرآن في مصحف واحد؟</t>
+          <t>في أي شهر نزل القرآن؟ | هل نزل القرآن مفرقاً؟ | متى جُمع القرآن في مصحف واحد؟ | من كان يكتب الوحي؟</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4897,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>لماذا جمع عثمان القرآن؟ | هل ضاع شيء من القرآن بجمع عثمان؟ | ما الفرق بين جمع أبي بكر وجمع عثمان؟</t>
+          <t>لماذا جمع عثمان القرآن؟ | هل ضاع شيء من القرآن بجمع عثمان؟ | لماذا جمع عثمان الناس على مصحف واحد؟</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -4859,16 +4927,21 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير. «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S7" s="7">
         <f>IF(A7="","",IF(OR(M7="ج",M7="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D7,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B7="",E7="",J7="",K7="",P7=""),"بيانات ناقصة",IF(AND(N7="نعم",Q7&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>كيف كُتب القرآن زمن النبي؟ | ما القراءات؟</t>
+          <t>كيف كُتب القرآن زمن النبي؟ | ما القراءات؟ | ما الفرق بين جمع أبي بكر وجمع عثمان؟</t>
         </is>
       </c>
     </row>
@@ -4963,12 +5036,17 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S8" s="7">
         <f>IF(A8="","",IF(OR(M8="ج",M8="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D8,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B8="",E8="",J8="",K8="",P8=""),"بيانات ناقصة",IF(AND(N8="نعم",Q8&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
       </c>
       <c r="U8" s="7" t="inlineStr">
         <is>
@@ -5068,12 +5146,17 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S9" s="7">
         <f>IF(A9="","",IF(OR(M9="ج",M9="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D9,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B9="",E9="",J9="",K9="",P9=""),"بيانات ناقصة",IF(AND(N9="نعم",Q9&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
@@ -5370,12 +5453,17 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S12" s="7">
         <f>IF(A12="","",IF(OR(M12="ج",M12="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D12,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B12="",E12="",J12="",K12="",P12=""),"بيانات ناقصة",IF(AND(N12="نعم",Q12&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
@@ -5474,13 +5562,18 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S13" s="7">
         <f>IF(A13="","",IF(OR(M13="ج",M13="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D13,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B13="",E13="",J13="",K13="",P13=""),"بيانات ناقصة",IF(AND(N13="نعم",Q13&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
           <t>ما هو القرآن؟ | ما مكانة القرآن؟ | كيف كان الوحي ينزل؟</t>
@@ -5576,13 +5669,18 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S14" s="7">
         <f>IF(A14="","",IF(OR(M14="ج",M14="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D14,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B14="",E14="",J14="",K14="",P14=""),"بيانات ناقصة",IF(AND(N14="نعم",Q14&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
           <t>ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟</t>
@@ -5677,13 +5775,18 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S15" s="7">
         <f>IF(A15="","",IF(OR(M15="ج",M15="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D15,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B15="",E15="",J15="",K15="",P15=""),"بيانات ناقصة",IF(AND(N15="نعم",Q15&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
       </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
           <t>كيف جُمع القرآن؟ | ما أسباب نزول آية بعينها؟</t>
@@ -5780,12 +5883,17 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
         </is>
       </c>
       <c r="S16" s="7">
         <f>IF(A16="","",IF(OR(M16="ج",M16="د"),"المستوى لا يُنشر",IF(IFERROR(INDEX(المصادر!$F$2:$F$30,MATCH(D16,المصادر!$A$2:$A$30,0)),"")&lt;&gt;"نعم","المصدر غير معتمد",IF(OR(B16="",E16="",J16="",K16="",P16=""),"بيانات ناقصة",IF(AND(N16="نعم",Q16&lt;&gt;"موافق"),"ينقصه رأي المختص","صالح للنشر")))))</f>
         <v/>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
         <is>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -705,7 +705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:X53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4142,6 +4142,52 @@
       <c r="V52" s="6" t="n"/>
       <c r="W52" s="6" t="n"/>
       <c r="X52" s="6" t="n"/>
+    </row>
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>ست-05</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>سؤال «من كتب القرآن؟»: المصدر أم كتّاب الوحي</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n"/>
+      <c r="F53" s="6" t="n"/>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="n"/>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>هل تسأل من أين جاء القرآن ولماذا يؤمن المسلمون أنه كلام الله، أم من كان يكتبه ويحفظه في عهد النبي ﷺ؟</t>
+        </is>
+      </c>
+      <c r="L53" s="6" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="6" t="n"/>
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="6" t="n"/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>استيضاح ثابت بين ح7 وح3 (ملاحظة المراجعة الحية). مراجعة شرعية: نعم.</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="n"/>
+      <c r="S53" s="6" t="n"/>
+      <c r="T53" s="6" t="n"/>
+      <c r="U53" s="6" t="n"/>
+      <c r="V53" s="6" t="n"/>
+      <c r="W53" s="6" t="n"/>
+      <c r="X53" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V49"/>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -940,7 +940,54 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1"/>
+    <row r="2" ht="150" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>قالب</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>و-16</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>تحت المقطع الذي حكم الفحص بأنه يجيب عن جزء من السؤال فقط (عنوانه «مقطع متعلق بسؤالك»)</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" s="11" t="n"/>
+      <c r="G2" s="11" t="n"/>
+      <c r="H2" s="11" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="11" t="n"/>
+      <c r="K2" s="11" t="inlineStr">
+        <is>
+          <t>قد لا يجيب هذا النص عن سؤالك كله. إن بقي منه شيء فاختر «جزئياً» واكتب ما بقي.</t>
+        </is>
+      </c>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="11" t="n"/>
+      <c r="P2" s="11" t="n"/>
+      <c r="Q2" s="11" t="inlineStr">
+        <is>
+          <t>نص واجهة، لا يحتاج مراجعة شرعية. يطابق ما تطلبه المنهجية: الجواب الجزئي يصرّح بحدوده.</t>
+        </is>
+      </c>
+      <c r="R2" s="11" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="11" t="n"/>
+      <c r="U2" s="11" t="n"/>
+      <c r="V2" s="11" t="n"/>
+      <c r="W2" s="11" t="n"/>
+      <c r="X2" s="11" t="n"/>
+      <c r="Y2" s="11" t="n"/>
+      <c r="Z2" s="11" t="n"/>
+    </row>
     <row r="3" ht="150" customHeight="1"/>
     <row r="4" ht="150" customHeight="1"/>
     <row r="5" ht="150" customHeight="1"/>
@@ -998,8 +1045,11 @@
     <cfRule type="expression" priority="3" dxfId="4">
       <formula>$O2="نعم"</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" dxfId="4">
+      <formula>$O2="نعم"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="7">
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
     </dataValidation>
@@ -1008,6 +1058,12 @@
     </dataValidation>
     <dataValidation sqref="W2:W300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"موافق,موافق بتعديل,غير موافق"</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -940,54 +940,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="150" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>قالب</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>و-16</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>تحت المقطع الذي حكم الفحص بأنه يجيب عن جزء من السؤال فقط (عنوانه «مقطع متعلق بسؤالك»)</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="11" t="inlineStr">
-        <is>
-          <t>قد لا يجيب هذا النص عن سؤالك كله. إن بقي منه شيء فاختر «جزئياً» واكتب ما بقي.</t>
-        </is>
-      </c>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
-      <c r="N2" s="11" t="n"/>
-      <c r="O2" s="11" t="n"/>
-      <c r="P2" s="11" t="n"/>
-      <c r="Q2" s="11" t="inlineStr">
-        <is>
-          <t>نص واجهة، لا يحتاج مراجعة شرعية. يطابق ما تطلبه المنهجية: الجواب الجزئي يصرّح بحدوده.</t>
-        </is>
-      </c>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="11" t="n"/>
-      <c r="U2" s="11" t="n"/>
-      <c r="V2" s="11" t="n"/>
-      <c r="W2" s="11" t="n"/>
-      <c r="X2" s="11" t="n"/>
-      <c r="Y2" s="11" t="n"/>
-      <c r="Z2" s="11" t="n"/>
-    </row>
+    <row r="2" ht="150" customHeight="1"/>
     <row r="3" ht="150" customHeight="1"/>
     <row r="4" ht="150" customHeight="1"/>
     <row r="5" ht="150" customHeight="1"/>
@@ -1048,8 +1001,11 @@
     <cfRule type="expression" priority="4" dxfId="4">
       <formula>$O2="نعم"</formula>
     </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>$O2="نعم"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
+  <dataValidations count="9">
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
     </dataValidation>
@@ -1058,6 +1014,12 @@
     </dataValidation>
     <dataValidation sqref="W2:W300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"نعم,لا"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
+    </dataValidation>
+    <dataValidation sqref="V2:V300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"موافق,موافق بتعديل,غير موافق"</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"معتمد,معتمد بتعديل,مرفوض"</formula1>
@@ -4651,12 +4613,18 @@
     <cfRule type="expression" priority="3" dxfId="5">
       <formula>$S2="صالح للنشر"</formula>
     </cfRule>
+    <cfRule type="expression" priority="5" dxfId="5">
+      <formula>$S2="صالح للنشر"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N2:N200">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>$N2="نعم"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="4">
+      <formula>$N2="نعم"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4">
       <formula>$N2="نعم"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4676,7 +4644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5770,6 +5738,38 @@
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>اعتُمد دون ملاحظات.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>و-16</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>تحت المقطع الذي حكم الفحص بأنه يجيب عن جزء من السؤال فقط (عنوانه «مقطع متعلق بسؤالك»)</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>قد لا يجيب هذا النص عن سؤالك كله. إن بقي منه شيء فاختر «جزئياً» واكتب ما بقي.</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>اعتُمد دون ملاحظات.</t>
         </is>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير. «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). [5 أكتوبر] عُدّلت بيانات التوجيه بعد مراجعة اللجنة الخارجية؛ النص المعتمد لم يتغير. «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة). [5 أكتوبر] أُضيفت صياغة «لماذا جمع عثمان القرآن؟» من ق-33 (موافقة محمد).</t>
         </is>
       </c>
       <c r="S7" s="7">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>كم عدد الصحابة الذين حفظوا القرآن؟ | هل نُقل القرآن عن عدد قليل؟ | كيف وصل القرآن إلينا؟</t>
+          <t>كم عدد الصحابة الذين حفظوا القرآن؟ | هل نُقل القرآن عن عدد قليل؟</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة).</t>
+          <t>مراجعة النقل: مطابق دون ملاحظات. مقطع حساس: وافق المختص الأعلم دون تعديل (2026-10-04). «لا يُجتزأ»: مقطع حجاجي يُعرض كاملاً حتى لا تُقتطع نتيجة دون حجتها (ملاحظة اللجنة). [5 أكتوبر] نُقلت صياغة «كيف وصل القرآن إلينا؟» إلى ق-33 بعد قياس السجل (موافقة محمد).</t>
         </is>
       </c>
       <c r="S8" s="7">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="L18" s="11" t="inlineStr">
         <is>
-          <t>ما مكانة القرآن عند المسلمين؟ | لماذا يعظّم المسلمون القرآن؟ | ما فائدة القرآن للإنسان؟ | لماذا يقرأ المسلمون القرآن كثيراً؟</t>
+          <t>ما مكانة القرآن عند المسلمين؟ | لماذا يعظّم المسلمون القرآن؟ | ما فائدة القرآن للإنسان؟</t>
         </is>
       </c>
       <c r="M18" s="11" t="inlineStr">
@@ -2938,7 +2938,7 @@
       <c r="Q18" s="11" t="n"/>
       <c r="R18" s="11" t="inlineStr">
         <is>
-          <t>اعتُمد دون ملاحظات.</t>
+          <t>اعتُمد دون ملاحظات. [5 أكتوبر] نُقلت صياغة «لماذا يقرأ المسلمون القرآن كثيراً؟» إلى ق-36 بعد قياس السجل (موافقة محمد).</t>
         </is>
       </c>
       <c r="S18" s="12">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L25" s="11" t="inlineStr">
         <is>
-          <t>كيف جُمع القرآن؟ | متى صار القرآن كتاباً واحداً؟ | لماذا جمع أبو بكر القرآن؟ | لماذا جمع عثمان القرآن؟ | هل تغيّر القرآن منذ زمن الصحابة؟</t>
+          <t>كيف جُمع القرآن؟ | متى صار القرآن كتاباً واحداً؟ | لماذا جمع أبو بكر القرآن؟ | هل تغيّر القرآن منذ زمن الصحابة؟ | كيف وصل القرآن إلينا؟</t>
         </is>
       </c>
       <c r="M25" s="11" t="inlineStr">
@@ -3598,7 +3598,7 @@
       <c r="Q25" s="11" t="n"/>
       <c r="R25" s="11" t="inlineStr">
         <is>
-          <t>اعتُمد دون ملاحظات.</t>
+          <t>اعتُمد دون ملاحظات. [5 أكتوبر] أُضيفت صياغة «كيف وصل القرآن إلينا؟» من ق-14 (موافقة محمد). [5 أكتوبر] نُقلت صياغة «لماذا جمع عثمان القرآن؟» إلى ق-13 بعد قياس السجل (موافقة محمد).</t>
         </is>
       </c>
       <c r="S25" s="12">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>ما فضل قراءة القرآن؟ | لماذا أقرأ القرآن؟ | هل في قراءة القرآن أجر؟ | ما فائدة الاجتماع على القرآن؟</t>
+          <t>ما فضل قراءة القرآن؟ | لماذا أقرأ القرآن؟ | هل في قراءة القرآن أجر؟ | ما فائدة الاجتماع على القرآن؟ | لماذا يقرأ المسلمون القرآن كثيراً؟</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
@@ -3783,7 +3783,7 @@
       <c r="Q27" s="11" t="n"/>
       <c r="R27" s="11" t="inlineStr">
         <is>
-          <t>اعتُمد دون ملاحظات.</t>
+          <t>اعتُمد دون ملاحظات. [5 أكتوبر] أُضيفت صياغة «لماذا يقرأ المسلمون القرآن كثيراً؟» من ق-02 (موافقة محمد).</t>
         </is>
       </c>
       <c r="S27" s="12">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>ليش السور مو مرتبة حسب نزولها؟ | من رتب سور القرآن؟ | هل ترتيب الآيات من النبي؟ | ليش البقرة أول القرآن مع إنها مدنية؟</t>
+          <t>ليش السور مو مرتبة حسب نزولها؟ | من رتب سور القرآن؟ | هل ترتيب الآيات من النبي؟</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
@@ -4376,7 +4376,7 @@
       <c r="Q33" s="11" t="n"/>
       <c r="R33" s="11" t="inlineStr">
         <is>
-          <t>نُفّذ: جملة المراجع تظهر سطراً مستقلاً بعنوان «تنبيه المراجع» لا داخل الاقتباس.</t>
+          <t>نُفّذ: جملة المراجع تظهر سطراً مستقلاً بعنوان «تنبيه المراجع» لا داخل الاقتباس. [5 أكتوبر] حُذفت صياغة «ليش البقرة أول القرآن مع إنها مدنية؟» لأن النص لا يذكر البقرة (موافقة محمد).</t>
         </is>
       </c>
       <c r="S33" s="12">

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="B10" s="33" t="inlineStr">
         <is>
-          <t>34 مقطعاً · 7 احتياجات · 5 مصادر/مراجع · 39 قالب محادثة (منها ست-06 بخياراتها الثلاثة، وام-14، وو-16)</t>
+          <t>34 مقطعاً · 7 احتياجات · 5 مصادر/مراجع · 40 قالب محادثة (منها ست-06 بخياراتها الثلاثة، وام-14، وام-15، وو-16)</t>
         </is>
       </c>
       <c r="C10" s="33" t="str"/>
@@ -7277,8 +7277,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:AH2"/>
+    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="AB3:AH3"/>
     <mergeCell ref="A1:AH1"/>
     <mergeCell ref="E3:M3"/>
@@ -8299,7 +8299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10016,6 +10016,48 @@
         </is>
       </c>
       <c r="H43" s="37" t="inlineStr">
+        <is>
+          <t>اعتمده محمد نصاً في المحادثة (5 أكتوبر 2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="58" customHeight="1">
+      <c r="A44" s="37" t="inlineStr">
+        <is>
+          <t>ام-15</t>
+        </is>
+      </c>
+      <c r="B44" s="37" t="inlineStr">
+        <is>
+          <t>NOT_COVERED</t>
+        </is>
+      </c>
+      <c r="C44" s="37" t="inlineStr">
+        <is>
+          <t>«المعنى غير واضح» بلا تفصيل ولا محتوى مرتبط</t>
+        </is>
+      </c>
+      <c r="D44" s="37" t="inlineStr">
+        <is>
+          <t>بعد «لا» أو «جزئياً» حين يختار المستخدم «المعنى غير واضح»، وليس للمقطع تفصيل لم يُعرض ولا محتوى مرتبط مسجّل</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="inlineStr">
+        <is>
+          <t>لا تحتوي مكتبة «دليل» حاليًا شرحًا أبسط لهذه النقطة. يمكنك الرجوع إلى مصدر موثوق يشرحها بمزيد من التبسيط، أو سؤال معلّم أو مختص.</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G44" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H44" s="37" t="inlineStr">
         <is>
           <t>اعتمده محمد نصاً في المحادثة (5 أكتوبر 2026).</t>
         </is>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -4,16 +4,17 @@
   <workbookPr/>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المحتوى المهيكل" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الاحتياجات" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المصادر" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منطق المحادثة" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="للمراجعة" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المرفوض" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الناقص" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التغطية والفجوات" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاموس المنهجية" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تدقيق 34" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="سجل التغييرات" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المحتوى المهيكل" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الاحتياجات" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المصادر" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منطق المحادثة" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="للمراجعة" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المرفوض" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الناقص" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التغطية والفجوات" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="قاموس المنهجية" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تدقيق 34" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -866,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="49" min="1" max="1"/>
@@ -901,7 +902,6 @@
       <c r="E2" s="1" t="n"/>
       <c r="F2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -1051,6 +1051,30 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>v22 (5 أكتوبر 2026): تدقيق المقاطع الـ34 (ورقة «تدقيق 34»): 12 مقطعاً عُدّلت بياناتها الوصفية فقط، ولم يتغير أي نص مرجعي. دُمج القالب ام-15، وحُذف «هل القرآن مثل الإنجيل عند المسيحيين؟» من صياغات ح1 النشطة ونُقل إلى الفجوات. أرقام v21 لا تنتقل إلى هذه النسخة إلا بقياس جديد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>الحوكمة</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>جميع مصادر المحتوى في هذه النسخة معتمدة. المراجعة المسجلة لبعض المقاطع تتعلق بسلامة النقل والتجزئة والسياق وحدود استخدام المقتطف، ولا تعني بالضرورة مراجعة شرعية مستقلة لمضمون المصدر من الصفر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>النسخة v23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>v23 (المرشحة النهائية، 5 أكتوبر 2026): v22 + قرارات المنع والاستيضاح الأخيرة (ق-14، ق-25، ق-06)، وقالبا استيضاح مرجعيان غير مفعّلين (ست-07، ست-08)، وفجوات جديدة، و«سجل التغييرات». صفر تغييرات في النص المرجعي. القاعدة: المنع لما لا يصلح للسؤال أصلاً؛ PARTIAL لما يفيد دون أن يكمل؛ CLARIFY لما يحتمل معنى يجيب عنه المقطع ومعنى لا يجيب عنه.</t>
         </is>
       </c>
     </row>
@@ -1064,6 +1088,1106 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="49" min="1" max="1"/>
+    <col width="38" customWidth="1" style="49" min="2" max="2"/>
+    <col width="25" customWidth="1" style="49" min="3" max="3"/>
+    <col width="12" customWidth="1" style="49" min="4" max="4"/>
+    <col width="55" customWidth="1" style="49" min="5" max="5"/>
+    <col width="18" customWidth="1" style="49" min="6" max="6"/>
+    <col width="45" customWidth="1" style="49" min="7" max="7"/>
+    <col width="14" customWidth="1" style="49" min="8" max="8"/>
+    <col width="14" customWidth="1" style="49" min="9" max="9"/>
+    <col width="14" customWidth="1" style="49" min="10" max="10"/>
+    <col width="48" customWidth="1" style="49" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Coverage Map — مصفوفة التغطية وفجوات النسخة الحالية</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>العدد لا يعني جودة التغطية وحده؛ الفجوات أدناه مبنية على مقارنة صياغات الاحتياجات بما تجيب عنه المقاطع وما تستبعده صراحة.</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>الحاجة</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>عدد المقاطع</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>تعريف</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>شرح</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>تعليم</t>
+        </is>
+      </c>
+      <c r="F4" s="63" t="inlineStr">
+        <is>
+          <t>استدلال</t>
+        </is>
+      </c>
+      <c r="G4" s="63" t="inlineStr">
+        <is>
+          <t>معالجة اعتراض</t>
+        </is>
+      </c>
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>مقارنة</t>
+        </is>
+      </c>
+      <c r="I4" s="63" t="inlineStr">
+        <is>
+          <t>بحث أو تحقيق</t>
+        </is>
+      </c>
+      <c r="J4" s="63" t="inlineStr">
+        <is>
+          <t>توجيه عملي</t>
+        </is>
+      </c>
+      <c r="K4" s="63" t="inlineStr">
+        <is>
+          <t>الحكم</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="B5" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="67" t="inlineStr">
+        <is>
+          <t>جيد؛ بقيت فجوتان: مقارنة مباشرة بين القرآن والحديث النبوي، والمقارنة العامة بين دور القرآن والإنجيل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="67" t="inlineStr">
+        <is>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="B6" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="67" t="inlineStr">
+        <is>
+          <t>جيد في عرض الموضوعات والقصص؛ لا يغطي استدلالاً مستقلاً على تاريخية القصص.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="67" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="B7" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="67" t="inlineStr">
+        <is>
+          <t>جيد؛ بقيت فجوات في تعريف الوحي المباشر، ومدة النزول، وأول ما نزل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="67" t="inlineStr">
+        <is>
+          <t>ح3</t>
+        </is>
+      </c>
+      <c r="B8" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="67" t="inlineStr">
+        <is>
+          <t>جيد؛ المقارنة المباشرة بين جمع أبي بكر وجمع عثمان تغطيتها جزئية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="67" t="inlineStr">
+        <is>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="B9" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="67" t="inlineStr">
+        <is>
+          <t>غير مكتمل عملياً؛ تعريف البنية موجود لكن الوصول إلى آية/جزء محدد غير مغطى.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="67" t="inlineStr">
+        <is>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="B10" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="67" t="inlineStr">
+        <is>
+          <t>غير مكتمل عملياً؛ توجد مواد للفهم والفضل والترجمة، لكن نقطة البداية واختيار تفسير للمبتدئ غير مغطاتين.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="67" t="inlineStr">
+        <is>
+          <t>ح7</t>
+        </is>
+      </c>
+      <c r="B11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="67" t="inlineStr">
+        <is>
+          <t>جيد في الاستدلال والاعتراضات؛ بقيت فجوة فرعية في سؤال معرفة النبي ﷺ بالقراءة والكتابة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>فجوات واضحة تحتاج محتوى أو معالجة صريحة</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="1" t="n"/>
+      <c r="E15" s="1" t="n"/>
+      <c r="F15" s="1" t="n"/>
+      <c r="G15" s="1" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="63" t="inlineStr">
+        <is>
+          <t>الحاجة</t>
+        </is>
+      </c>
+      <c r="B16" s="63" t="inlineStr">
+        <is>
+          <t>السؤال/الفجوة</t>
+        </is>
+      </c>
+      <c r="C16" s="63" t="inlineStr">
+        <is>
+          <t>نوع الفجوة</t>
+        </is>
+      </c>
+      <c r="D16" s="63" t="inlineStr">
+        <is>
+          <t>الأولوية</t>
+        </is>
+      </c>
+      <c r="E16" s="63" t="inlineStr">
+        <is>
+          <t>الدليل من السجل</t>
+        </is>
+      </c>
+      <c r="F16" s="63" t="inlineStr">
+        <is>
+          <t>الحالة</t>
+        </is>
+      </c>
+      <c r="G16" s="63" t="inlineStr">
+        <is>
+          <t>الإجراء الهيكلي</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" s="49">
+      <c r="A17" s="67" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>ما الفرق بين القرآن والحديث؟</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>تغطية مباشرة مفقودة</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>ق-35 يستبعد الفرق الشامل بين القرآن والحديث النبوي؛ ق-32 يعالج حجية السنة.</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى مباشرة</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقطع مقارنة مباشر أو إعلان عدم التغطية.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" s="49">
+      <c r="A18" s="67" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>كم سنة استمر نزول القرآن؟</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>معلومة تأسيسية مفقودة</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>مذكور ضمن صياغات الحاجة ح2 ولا يوجد مقطع يجيب عنها مباشرة.</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقتطف موثق مباشر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" s="49">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="B19" s="67" t="inlineStr">
+        <is>
+          <t>ما أول آية نزلت؟</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="inlineStr">
+        <is>
+          <t>معلومة تأسيسية مفقودة</t>
+        </is>
+      </c>
+      <c r="D19" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="inlineStr">
+        <is>
+          <t>مذكور ضمن صياغات الحاجة ح2 ولا يوجد مقطع يجيب عنها مباشرة.</t>
+        </is>
+      </c>
+      <c r="F19" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقتطف موثق مباشر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" s="49">
+      <c r="A20" s="67" t="inlineStr">
+        <is>
+          <t>ح3</t>
+        </is>
+      </c>
+      <c r="B20" s="67" t="inlineStr">
+        <is>
+          <t>ما الفرق بين جمع أبي بكر وجمع عثمان؟</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="inlineStr">
+        <is>
+          <t>مقارنة جزئية</t>
+        </is>
+      </c>
+      <c r="D20" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="inlineStr">
+        <is>
+          <t>ق-13 يذكر صراحة أنه لا يجيب عن المقارنة؛ ق-33 يعرض المراحل دون مقارنة مركزة.</t>
+        </is>
+      </c>
+      <c r="F20" s="67" t="inlineStr">
+        <is>
+          <t>جزئي</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقارنة قصيرة أو PARTIAL بحدود واضحة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" s="49">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="B21" s="67" t="inlineStr">
+        <is>
+          <t>كيف أجد آية في المصحف؟</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="inlineStr">
+        <is>
+          <t>تعليم عملي مفقود</t>
+        </is>
+      </c>
+      <c r="D21" s="67" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="inlineStr">
+        <is>
+          <t>ق-15 يسجلها ضمن الأسئلة القريبة التي لا يجيب عنها.</t>
+        </is>
+      </c>
+      <c r="F21" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقطع/إرشاد عملي مستقل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" s="49">
+      <c r="A22" s="67" t="inlineStr">
+        <is>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="B22" s="67" t="inlineStr">
+        <is>
+          <t>ما معنى جزء عمّ؟</t>
+        </is>
+      </c>
+      <c r="C22" s="67" t="inlineStr">
+        <is>
+          <t>تعريف عملي مفقود</t>
+        </is>
+      </c>
+      <c r="D22" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="inlineStr">
+        <is>
+          <t>مذكور ضمن صياغات الحاجة ح4 ولا يوجد مقطع مباشر.</t>
+        </is>
+      </c>
+      <c r="F22" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقتطف تعريفي مباشر.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" s="49">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>ح4</t>
+        </is>
+      </c>
+      <c r="B23" s="67" t="inlineStr">
+        <is>
+          <t>كيف أعرف رقم الآية؟</t>
+        </is>
+      </c>
+      <c r="C23" s="67" t="inlineStr">
+        <is>
+          <t>تعليم عملي مفقود</t>
+        </is>
+      </c>
+      <c r="D23" s="67" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="inlineStr">
+        <is>
+          <t>مذكور ضمن صياغات الحاجة ح4 ولا يوجد مقطع مباشر.</t>
+        </is>
+      </c>
+      <c r="F23" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G23" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقطع/إرشاد عملي مستقل.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" s="49">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="B24" s="67" t="inlineStr">
+        <is>
+          <t>من أين أبدأ قراءة القرآن؟</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>توجيه عملي مفقود</t>
+        </is>
+      </c>
+      <c r="D24" s="67" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>ق-18 في ورقة «الناقص» الأصلية: من أين يبدأ المبتدئ القراءة.</t>
+        </is>
+      </c>
+      <c r="F24" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مادة بداية عملية قبل التجميد.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" s="49">
+      <c r="A25" s="67" t="inlineStr">
+        <is>
+          <t>ح6</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>ما أفضل تفسير للمبتدئ؟</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>توجيه مصدر مفقود</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>ق-19 يسجل السؤال ضمن الأسئلة القريبة التي لا يجيب عنها.</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>إضافة توصية مصدر مراجعة وفق سياسة المرجعية أو إحالة مضبوطة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" s="49">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>ح7</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>هل كان النبي يعرف القراءة والكتابة؟</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
+        <is>
+          <t>استدلال فرعي مفقود</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="inlineStr">
+        <is>
+          <t>مذكور ضمن صياغات الحاجة ح7 ولا يوجد مقطع يجيب عنه مباشرة.</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>إضافة مقتطف موثق إذا سيبقى السؤال ضمن الوعود النشطة.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1" s="49">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>هل القرآن مثل الإنجيل عند المسيحيين؟</t>
+        </is>
+      </c>
+      <c r="C27" s="94" t="inlineStr">
+        <is>
+          <t>مقارنة عامة ملتبسة وغير مغطاة مباشرة</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E27" s="94" t="inlineStr">
+        <is>
+          <t>ق-03 يشرح علاقة القرآن بالكتب السابقة، لا المقارنة بين دور القرآن عند المسلمين ودور الإنجيل عند المسيحيين.</t>
+        </is>
+      </c>
+      <c r="F27" s="94" t="inlineStr">
+        <is>
+          <t>غير مغطى مباشرة</t>
+        </is>
+      </c>
+      <c r="G27" s="94" t="inlineStr">
+        <is>
+          <t>CLARIFY حسب المقصود، أو NOT_COVERED إذا كان المقصود مقارنة الدور الديني العامة.</t>
+        </is>
+      </c>
+      <c r="H27" s="94" t="n"/>
+      <c r="I27" s="94" t="n"/>
+      <c r="J27" s="94" t="n"/>
+      <c r="K27" s="94" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1" s="49">
+      <c r="A28" s="93" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="B28" s="93" t="inlineStr">
+        <is>
+          <t>ما هو الوحي؟</t>
+        </is>
+      </c>
+      <c r="C28" s="93" t="inlineStr">
+        <is>
+          <t>تعريف تأسيسي غير مباشر</t>
+        </is>
+      </c>
+      <c r="D28" s="93" t="inlineStr">
+        <is>
+          <t>عالية</t>
+        </is>
+      </c>
+      <c r="E28" s="93" t="inlineStr">
+        <is>
+          <t>ق-08 يشرح صور مجيء الوحي للنبي ﷺ، لكنه لا يقدم تعريفاً تمهيدياً مستقلاً لمفهوم الوحي.</t>
+        </is>
+      </c>
+      <c r="F28" s="93" t="inlineStr">
+        <is>
+          <t>جزئي</t>
+        </is>
+      </c>
+      <c r="G28" s="93" t="inlineStr">
+        <is>
+          <t>PARTIAL أو إضافة تعريف مباشر قبل توسيع الوعد.</t>
+        </is>
+      </c>
+      <c r="H28" s="93" t="n"/>
+      <c r="I28" s="93" t="n"/>
+      <c r="J28" s="93" t="n"/>
+      <c r="K28" s="93" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1" s="49">
+      <c r="A29" s="94" t="inlineStr">
+        <is>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="B29" s="94" t="inlineStr">
+        <is>
+          <t>كيف نعرف أن قصص القرآن حقيقية؟</t>
+        </is>
+      </c>
+      <c r="C29" s="94" t="inlineStr">
+        <is>
+          <t>استدلال/اعتراض غير مغطى</t>
+        </is>
+      </c>
+      <c r="D29" s="94" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E29" s="94" t="inlineStr">
+        <is>
+          <t>ق-06 يعرّف القصص وأنواعها وغاياتها، لكنه لا يقدم دليلاً مستقلاً لمن يطلب إثبات تاريخيتها.</t>
+        </is>
+      </c>
+      <c r="F29" s="94" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G29" s="94" t="inlineStr">
+        <is>
+          <t>NOT_COVERED ضمن النسخة الحالية ما لم تضاف مادة استدلالية مستقلة.</t>
+        </is>
+      </c>
+      <c r="H29" s="94" t="n"/>
+      <c r="I29" s="94" t="n"/>
+      <c r="J29" s="94" t="n"/>
+      <c r="K29" s="94" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="95" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="B30" s="95" t="inlineStr">
+        <is>
+          <t>هل القرآن مثل الإنجيل عند المسيحيين؟</t>
+        </is>
+      </c>
+      <c r="C30" s="95" t="inlineStr">
+        <is>
+          <t>مقارنة غير مغطاة</t>
+        </is>
+      </c>
+      <c r="D30" s="95" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E30" s="95" t="inlineStr">
+        <is>
+          <t>v22: ق-03 يستبعدها صراحة؛ يجيب عن صلة القرآن بالكتب السابقة لا عن مقارنة دوره بدور الإنجيل.</t>
+        </is>
+      </c>
+      <c r="F30" s="95" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G30" s="95" t="inlineStr">
+        <is>
+          <t>حُذفت من صياغات ح1 النشطة؛ تُضاف مادة مقارنة مباشرة أو يبقى الامتناع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="95" t="inlineStr">
+        <is>
+          <t>ح2</t>
+        </is>
+      </c>
+      <c r="B31" s="95" t="inlineStr">
+        <is>
+          <t>ما هو الوحي؟ (تعريف تمهيدي مباشر)</t>
+        </is>
+      </c>
+      <c r="C31" s="95" t="inlineStr">
+        <is>
+          <t>تعريف مفقود</t>
+        </is>
+      </c>
+      <c r="D31" s="95" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E31" s="95" t="inlineStr">
+        <is>
+          <t>v22: حُذفت من صياغات ق-08؛ ق-08 يشرح صور الوحي لا تعريفه.</t>
+        </is>
+      </c>
+      <c r="F31" s="95" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G31" s="95" t="inlineStr">
+        <is>
+          <t>إضافة مقتطف تعريفي أو الامتناع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="95" t="inlineStr">
+        <is>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="B32" s="95" t="inlineStr">
+        <is>
+          <t>كيف نعرف أن قصص القرآن حقيقية؟ (إثبات تاريخيتها)</t>
+        </is>
+      </c>
+      <c r="C32" s="95" t="inlineStr">
+        <is>
+          <t>استدلال مفقود</t>
+        </is>
+      </c>
+      <c r="D32" s="95" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E32" s="95" t="inlineStr">
+        <is>
+          <t>ق-06 يعامل القصص وقائع ولا يقدم دليلاً مستقلاً؛ السؤال الأبسط PARTIAL بـ ق-06.</t>
+        </is>
+      </c>
+      <c r="F32" s="95" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G32" s="95" t="inlineStr">
+        <is>
+          <t>إضافة مادة استدلالية أو الامتناع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="95" t="inlineStr">
+        <is>
+          <t>ح7</t>
+        </is>
+      </c>
+      <c r="B33" s="95" t="inlineStr">
+        <is>
+          <t>لماذا تتشابه قصص القرآن مع الكتب السابقة؟</t>
+        </is>
+      </c>
+      <c r="C33" s="95" t="inlineStr">
+        <is>
+          <t>شرح مفقود</t>
+        </is>
+      </c>
+      <c r="D33" s="95" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E33" s="95" t="inlineStr">
+        <is>
+          <t>ق-25 يرد على دعوى الاقتباس ولا يشرح سبب التشابه (منع صريح في v23).</t>
+        </is>
+      </c>
+      <c r="F33" s="95" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G33" s="95" t="inlineStr">
+        <is>
+          <t>إضافة مادة أو الامتناع.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A15:G15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D17:D26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>D17="عالية"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1594,7 +2718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4256,6 +5380,999 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" style="49" min="1" max="1"/>
+    <col width="8" customWidth="1" style="49" min="2" max="2"/>
+    <col width="22" customWidth="1" style="49" min="3" max="3"/>
+    <col width="60" customWidth="1" style="49" min="4" max="4"/>
+    <col width="60" customWidth="1" style="49" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>النسخة</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المقطع</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحقل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>التغيير</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>السبب</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>النص المرجعي</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0 تغييرات في المقاطع الـ34</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>تدقيق «تدقيق 34»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ق-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>قبل: هل القرآن مثل الإنجيل عند المسيحيين؟ | ما علاقة القرآن بالتوراة والإنجيل؟ | ما معنى أن القرآن مهيمن؟ ← بعد: ما علاقة القرآن بالتوراة والإنجيل؟ | ما معنى أن القرآن مهيمن؟</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ق-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>قبل: يشرح صلة القرآن بالكتب السابقة إجمالاً، ولا يعالج وحده دعوى الاقتباس أو الفرق بين القرآن والحديث. ← بعد: يشرح صلة القرآن بالكتب السابقة إجمالاً، ولا يعالج وحده دعوى الاقتباس أو الفرق بين القرآن والحديث. ولا يقارن دور القرآن عند المسلمين بدور الإنجيل عند ا</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ق-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>قبل: هل نقل محمد القرآن من التوراة؟ | ما الفرق بين القرآن والحديث؟ ← بعد: هل نقل محمد القرآن من التوراة؟ | ما الفرق بين القرآن والحديث؟ | هل القرآن مثل الإنجيل عند المسيحيين؟</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ق-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>قبل: هل القرآن فيه قصص؟ | هل يذكر القرآن موسى وعيسى؟ | ليش القرآن يحكي قصص الأنبياء؟ | هل قصص القرآن حقيقية؟ ← بعد: هل القرآن فيه قصص؟ | هل يذكر القرآن موسى وعيسى؟ | ليش القرآن يحكي قصص الأنبياء؟</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ق-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>قبل: يبين وجود القصص في القرآن وغايتها إجمالاً، ولا يسرد قصة نبي بالتفصيل أو يناقش مصدر القصص. ← بعد: يبين وجود القصص في القرآن وغايتها إجمالاً، ولا يسرد قصة نبي بالتفصيل أو يناقش مصدر القصص. ولا يقدم استدلالاً مستقلاً على تاريخية القصص لمن يطلب إثباته</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ق-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>قبل: ما قصة نوح بالتفصيل؟ | هل قصص القرآن منقولة من التوراة؟ ← بعد: ما قصة نوح بالتفصيل؟ | هل قصص القرآن منقولة من التوراة؟ | كيف نعرف أن قصص القرآن حقيقية؟</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ق-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قبل: كيف كان الوحي يأتي النبي؟ | ما هو الوحي؟ | كيف وصل القرآن لمحمد؟ | كيف كان جبريل ينزل بالقرآن؟ | ما طرق نزول الوحي على النبي؟ | هل كان جبريل يأتي النب ← بعد: كيف كان الوحي يأتي النبي؟ | كيف وصل القرآن لمحمد؟ | كيف كان جبريل ينزل بالقرآن؟ | ما طرق نزول الوحي على النبي؟ | هل كان جبريل يأتي النبي في صورة رجل؟ </t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ق-08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>قبل: يشرح صور مجيء الوحي للنبي ﷺ، ولا يحدد زمن النزول أو يجيب عن حكمة خفاء الوحي. ← بعد: يشرح صور مجيء الوحي للنبي ﷺ، ولا يحدد زمن النزول أو يجيب عن حكمة خفاء الوحي. ولا يقدم تعريفاً تمهيدياً مستقلاً لمفهوم الوحي.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ق-09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>قبل: متى نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما علاقة القرآن برمضان؟ ← بعد: في أي شهر نزل القرآن؟ | ما علاقة القرآن برمضان؟</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ق-09</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PRIMARY_TASK</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>قبل: تعريف ← بعد: شرح</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ق-09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TASK_TYPES</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>قبل: شرح ← بعد: —</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ق-09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">قبل: يثبت ارتباط نزول القرآن برمضان، ولا يشرح صور الوحي أو كيفية النزول المفرق. ← بعد: يثبت ارتباط نزول القرآن برمضان، ولا يشرح صور الوحي أو كيفية النزول المفرق. والسؤال العام «متى نزل القرآن؟» يحتاج تحديد المقصود: الشهر أو بداية النزول </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ق-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>قبل: كم عدد الصحابة الذين حفظوا القرآن؟ | هل نُقل القرآن عن عدد قليل؟ ← بعد: هل نُقل القرآن عن عدد قليل؟</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ق-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>قبل: كيف جمع عثمان القرآن؟ | كيف أحفظ القرآن؟ ← بعد: كيف جمع عثمان القرآن؟ | كيف أحفظ القرآن؟ | كم كان عدد حفظة القرآن من الصحابة تحديداً؟</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ق-20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>قبل: هل الترجمة تعتبر قرآناً؟ | أقدر أقرأ القرآن بالإنجليزي؟ | ما الفرق بين القرآن وترجمة معانيه؟ | ليش يقولون ترجمة معاني القرآن؟ ← بعد: هل الترجمة تعتبر قرآناً؟ | ما الفرق بين القرآن وترجمة معانيه؟ | ليش يقولون ترجمة معاني القرآن؟</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ق-20</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>قبل: يبين الفرق بين القرآن وترجمة معانيه وحكم الترجمة الحرفية في النص، ولا يحدد أفضل ترجمة أو يفتي في الصلاة بالترجمة. ← بعد: يبين الفرق بين القرآن وترجمة معانيه وحكم الترجمة الحرفية في النص، ولا يحدد أفضل ترجمة أو يفتي في الصلاة بالترجمة. وصيغة «القراءة بالإنجليزية» ملتبسة ب</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ق-24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>قبل: ما هو القرآن؟ | ما مكانة القرآن؟ | كيف كان الوحي ينزل؟ ← بعد: ما هو القرآن؟ | ما مكانة القرآن؟ | كيف كان الوحي ينزل؟ | ما أمثلة الإعجاز العلمي؟</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ق-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>قبل: هل نقل محمد القرآن من التوراة والإنجيل؟ | لماذا تتشابه قصص القرآن مع الكتب السابقة؟ | هل القرآن مقتبس؟ ← بعد: هل نقل محمد القرآن من التوراة والإنجيل؟ | هل القرآن مقتبس؟</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ق-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>قبل: يعالج دعوى الاقتباس من الكتب السابقة إجمالاً، ولا يشرح كل أوجه التشابه أو تاريخ النصوص السابقة. ← بعد: يعالج دعوى الاقتباس من الكتب السابقة إجمالاً، ولا يشرح كل أوجه التشابه أو تاريخ النصوص السابقة. ولا يشرح سبب وجود أوجه تشابه بين بعض القصص؛ بل يعالج د</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ق-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>قبل: ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟ ← بعد: ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟ | ما سبب تشابه بعض قصص القرآن مع الكتب السابقة؟</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ق-26</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>قبل: كيف جُمع القرآن؟ | ما أسباب نزول آية بعينها؟ ← بعد: كيف جُمع القرآن؟ | ما أسباب نزول آية بعينها؟ | ما أمثلة الإعجاز العلمي؟</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ق-29</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>قبل: يعالج دعوى أن اختلاف اللين والشدة سببه تأثر بشري بالبيئة، ولا يشرح تعريف المكي والمدني ولا تاريخ النزول. ← بعد: يعالج دعوى أن اختلاف اللين والشدة سببه تأثر بشري بالبيئة، ولا يشرح تعريف المكي والمدني ولا تاريخ النزول. ولا يقدم مقارنة شاملة لجميع خصائص الأسلوب الم</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ق-29</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>قبل: كيف نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما معنى سورة مكية؟ | ما الفرق بين أسلوب السور المكية والمدنية؟ ← بعد: كيف نزل القرآن؟ | في أي شهر نزل القرآن؟ | ما معنى سورة مكية؟</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ق-32</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>قبل: يثبت حاجة الدين إلى السنة وحجيتها بوصفها مبيِّنة للقرآن، ولا يقدّم تفصيلاً في علوم الحديث أو حجية كل نوع من أنواع السنة. ← بعد: يثبت حاجة الدين إلى السنة وحجيتها بوصفها مبيِّنة للقرآن، ولا يقدّم تفصيلاً في علوم الحديث أو حجية كل نوع من أنواع السنة. وقد يفيد جزئياً في سؤال علاقة</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ق-32</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>قبل: ما علاقة القرآن بالكتب السابقة؟ | ما تعريف القرآن؟ | ما مكانة القرآن عند المسلمين؟ | ما علاقة الحديث بالقرآن؟ | ما الفرق بين القرآن والحديث؟ ← بعد: ما علاقة القرآن بالكتب السابقة؟ | ما تعريف القرآن؟ | ما مكانة القرآن عند المسلمين؟ | ما الفرق بين القرآن والحديث؟</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ق-37</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>قبل: هل نزل القرآن مرة واحدة؟ | لماذا نزل القرآن مفرّقاً؟ | كم مرة نزل القرآن؟ ← بعد: هل نزل القرآن مرة واحدة؟ | لماذا نزل القرآن مفرّقاً؟</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ق-37</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EVIDENCE_LIMITS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>قبل: يشرح أن القرآن نزل مفرقاً بحسب الوقائع، ولا يحدد شهر النزول أو صور مجيء الوحي. ← بعد: يشرح أن القرآن نزل مفرقاً بحسب الوقائع، ولا يحدد شهر النزول أو صور مجيء الوحي. ولا يحدد عدداً معيناً لمرات النزول.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ق-37</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>قبل: في أي شهر نزل القرآن؟ | كيف كان الوحي يأتي النبي؟ ← بعد: في أي شهر نزل القرآن؟ | كيف كان الوحي يأتي النبي؟ | كم مرة تحديداً نزل القرآن؟</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>تدقيق v22</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ق-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>أُضيف «ما الدليل على أن قصص القرآن حقيقية؟»</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>طلب الدليل NOT_COVERED؛ والسؤال الأبسط «هل قصص القرآن حقيقية؟» PARTIAL بلا منع</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ق-14</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>حُذف «كم كان عدد حفظة القرآن من الصحابة تحديداً؟»</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>السؤال عن العدد PARTIAL بـ ق-14 لا منع؛ والقيد في الحدود</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ق-25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>أُضيف «لماذا تتشابه قصص القرآن مع الكتب السابقة؟»</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NOT_COVERED: يرد على دعوى الاقتباس ولا يشرح سبب التشابه</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ح1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>أُعيد «هل القرآن مثل الإنجيل عند المسيحيين؟» موسوماً [فجوة]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>حاجة حقيقية غير مغطاة؛ لا تُصدَّر للموجّه</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>منطق المحادثة</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ست-07 وست-08 بخياراتهما (مرجعية، غير مفعّلة)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>الحقيقة المرجعية CLARIFY لـ«متى نزل القرآن؟» و«أقدر أقرأ بالإنجليزي؟»</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>v23</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>النص المرجعي</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0 تغييرات</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5826,7 +7943,7 @@
       </c>
       <c r="Y12" s="67" t="inlineStr">
         <is>
-          <t>ما قصة نوح بالتفصيل؟ | هل قصص القرآن منقولة من التوراة؟ | كيف نعرف أن قصص القرآن حقيقية؟</t>
+          <t>ما قصة نوح بالتفصيل؟ | هل قصص القرآن منقولة من التوراة؟ | كيف نعرف أن قصص القرآن حقيقية؟ | ما الدليل على أن قصص القرآن حقيقية؟</t>
         </is>
       </c>
       <c r="Z12" s="67" t="inlineStr">
@@ -7604,17 +9721,17 @@
       </c>
       <c r="W23" s="67" t="inlineStr">
         <is>
-          <t>يرد على دعوى قلة ناقلي القرآن ويبين كثرة الحفاظ، ولا يقدم إحصاءً حصرياً أو شرحاً كاملاً لعلم التواتر.</t>
+          <t>يرد على دعوى قلة ناقلي القرآن ويبين كثرة الحفاظ، ولا يقدم إحصاءً حصرياً أو شرحاً كاملاً لعلم التواتر. لا يقدم عددًا حصريًا محددًا لحفاظ القرآن من الصحابة.</t>
         </is>
       </c>
       <c r="X23" s="67" t="inlineStr">
         <is>
-          <t>لا يشرح جمع عثمان ولا كيفية حفظ القرآن عملياً.</t>
+          <t>لا يشرح جمع عثمان ولا كيفية حفظ القرآن عملياً. لا يقدم عددًا حصريًا محددًا لحفاظ القرآن من الصحابة.</t>
         </is>
       </c>
       <c r="Y23" s="67" t="inlineStr">
         <is>
-          <t>كيف جمع عثمان القرآن؟ | كيف أحفظ القرآن؟ | كم كان عدد حفظة القرآن من الصحابة تحديداً؟</t>
+          <t>كيف جمع عثمان القرآن؟ | كيف أحفظ القرآن؟</t>
         </is>
       </c>
       <c r="Z23" s="67" t="inlineStr">
@@ -9736,12 +11853,12 @@
       </c>
       <c r="X36" s="67" t="inlineStr">
         <is>
-          <t>لا يشرح معنى هيمنة القرآن على الكتب السابقة ولا يسرد قصص الأنبياء.</t>
+          <t>لا يشرح معنى هيمنة القرآن على الكتب السابقة ولا يسرد قصص الأنبياء. لا يشرح سبب أوجه التشابه بين بعض قصص القرآن والكتب السابقة.</t>
         </is>
       </c>
       <c r="Y36" s="67" t="inlineStr">
         <is>
-          <t>ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟ | ما سبب تشابه بعض قصص القرآن مع الكتب السابقة؟</t>
+          <t>ما معنى أن القرآن مهيمن على الكتب السابقة؟ | ما قصص الأنبياء في القرآن؟ | ما سبب تشابه بعض قصص القرآن مع الكتب السابقة؟ | لماذا تتشابه قصص القرآن مع الكتب السابقة؟</t>
         </is>
       </c>
       <c r="Z36" s="67" t="inlineStr">
@@ -10138,9 +12255,9 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:AH2"/>
-    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="AB3:AH3"/>
+    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="A1:AH1"/>
     <mergeCell ref="E3:M3"/>
   </mergeCells>
@@ -10161,7 +12278,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10335,7 +12452,7 @@
       </c>
       <c r="F5" s="67" t="inlineStr">
         <is>
-          <t>«ما هو القرآن؟» · «إيش يعني القرآن؟» · «ليش المسلمين يقدّسون القرآن؟» · «ما الفرق بين القرآن والحديث؟» · «لماذا يقرأ المسلمون القرآن كثيراً؟»</t>
+          <t>«ما هو القرآن؟» · «إيش يعني القرآن؟» · «ليش المسلمين يقدّسون القرآن؟» · «ما الفرق بين القرآن والحديث؟» · «لماذا يقرأ المسلمون القرآن كثيراً؟» · «هل القرآن مثل الإنجيل عند المسيحيين؟» [فجوة]</t>
         </is>
       </c>
       <c r="G5" s="67" t="inlineStr">
@@ -10844,7 +12961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11155,13 +13272,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="49" min="1" max="1"/>
@@ -12925,6 +15042,342 @@
         </is>
       </c>
     </row>
+    <row r="45" ht="58" customHeight="1" s="49">
+      <c r="A45" s="37" t="inlineStr">
+        <is>
+          <t>ست-07</t>
+        </is>
+      </c>
+      <c r="B45" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C45" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY: الشهر أو بداية النزول أو مدته</t>
+        </is>
+      </c>
+      <c r="D45" s="37" t="inlineStr">
+        <is>
+          <t>سؤال «متى نزل القرآن؟» العام</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="inlineStr">
+        <is>
+          <t>ماذا تقصد بـ«متى نزل القرآن»؟</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G45" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H45" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="58" customHeight="1" s="49">
+      <c r="A46" s="37" t="inlineStr">
+        <is>
+          <t>ست-07-1</t>
+        </is>
+      </c>
+      <c r="B46" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C46" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← ق-09</t>
+        </is>
+      </c>
+      <c r="D46" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الأول في ست-07 ← ق-09</t>
+        </is>
+      </c>
+      <c r="E46" s="37" t="inlineStr">
+        <is>
+          <t>في أي شهر نزل القرآن؟</t>
+        </is>
+      </c>
+      <c r="F46" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G46" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H46" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="58" customHeight="1" s="49">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>ست-07-2</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← غير مغطى</t>
+        </is>
+      </c>
+      <c r="D47" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الثاني في ست-07 ← NOT_COVERED حالياً</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="inlineStr">
+        <is>
+          <t>متى بدأ نزول القرآن أول مرة؟</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G47" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H47" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58" customHeight="1" s="49">
+      <c r="A48" s="37" t="inlineStr">
+        <is>
+          <t>ست-07-3</t>
+        </is>
+      </c>
+      <c r="B48" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C48" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← غير مغطى</t>
+        </is>
+      </c>
+      <c r="D48" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الثالث في ست-07 ← NOT_COVERED حالياً</t>
+        </is>
+      </c>
+      <c r="E48" s="37" t="inlineStr">
+        <is>
+          <t>كم سنة استمر نزول القرآن؟</t>
+        </is>
+      </c>
+      <c r="F48" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G48" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H48" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="58" customHeight="1" s="49">
+      <c r="A49" s="37" t="inlineStr">
+        <is>
+          <t>ست-08</t>
+        </is>
+      </c>
+      <c r="B49" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C49" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY: الفهم أو حكم الترجمة أو العبادة</t>
+        </is>
+      </c>
+      <c r="D49" s="37" t="inlineStr">
+        <is>
+          <t>سؤال «أقدر أقرأ القرآن بالإنجليزي؟» وما في معناه</t>
+        </is>
+      </c>
+      <c r="E49" s="37" t="inlineStr">
+        <is>
+          <t>ماذا تقصد بالقراءة بالإنجليزية؟</t>
+        </is>
+      </c>
+      <c r="F49" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G49" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H49" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58" customHeight="1" s="49">
+      <c r="A50" s="37" t="inlineStr">
+        <is>
+          <t>ست-08-1</t>
+        </is>
+      </c>
+      <c r="B50" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C50" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← ق-20</t>
+        </is>
+      </c>
+      <c r="D50" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الأول في ست-08 ← ق-20</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="inlineStr">
+        <is>
+          <t>قراءة ترجمة معاني القرآن للفهم؟</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G50" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H50" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="58" customHeight="1" s="49">
+      <c r="A51" s="37" t="inlineStr">
+        <is>
+          <t>ست-08-2</t>
+        </is>
+      </c>
+      <c r="B51" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C51" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← ق-20</t>
+        </is>
+      </c>
+      <c r="D51" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الثاني في ست-08 ← ق-20</t>
+        </is>
+      </c>
+      <c r="E51" s="37" t="inlineStr">
+        <is>
+          <t>هل الترجمة الإنجليزية نفسها تُعد قرآنًا؟</t>
+        </is>
+      </c>
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G51" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H51" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="58" customHeight="1" s="49">
+      <c r="A52" s="37" t="inlineStr">
+        <is>
+          <t>ست-08-3</t>
+        </is>
+      </c>
+      <c r="B52" s="37" t="inlineStr">
+        <is>
+          <t>CLARIFY (مرجعي)</t>
+        </is>
+      </c>
+      <c r="C52" s="37" t="inlineStr">
+        <is>
+          <t>خيار ← إحالة (ام-02)</t>
+        </is>
+      </c>
+      <c r="D52" s="37" t="inlineStr">
+        <is>
+          <t>الخيار الثالث في ست-08 ← REFER</t>
+        </is>
+      </c>
+      <c r="E52" s="37" t="inlineStr">
+        <is>
+          <t>القراءة بالإنجليزية في الصلاة أو العبادة؟</t>
+        </is>
+      </c>
+      <c r="F52" s="37" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="G52" s="37" t="inlineStr">
+        <is>
+          <t>محمد — 5 أكتوبر 2026</t>
+        </is>
+      </c>
+      <c r="H52" s="37" t="inlineStr">
+        <is>
+          <t>مرجعي — غير مفعّل برمجياً في v1.0؛ يحدد الحقيقة المرجعية (CLARIFY) ويُفعَّل في إصدار لاحق بعد قياس.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -12937,7 +15390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13124,7 +15577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13184,7 +15637,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13264,993 +15717,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" style="49" min="1" max="1"/>
-    <col width="38" customWidth="1" style="49" min="2" max="2"/>
-    <col width="25" customWidth="1" style="49" min="3" max="3"/>
-    <col width="12" customWidth="1" style="49" min="4" max="4"/>
-    <col width="55" customWidth="1" style="49" min="5" max="5"/>
-    <col width="18" customWidth="1" style="49" min="6" max="6"/>
-    <col width="45" customWidth="1" style="49" min="7" max="7"/>
-    <col width="14" customWidth="1" style="49" min="8" max="8"/>
-    <col width="14" customWidth="1" style="49" min="9" max="9"/>
-    <col width="14" customWidth="1" style="49" min="10" max="10"/>
-    <col width="48" customWidth="1" style="49" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Coverage Map — مصفوفة التغطية وفجوات النسخة الحالية</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>العدد لا يعني جودة التغطية وحده؛ الفجوات أدناه مبنية على مقارنة صياغات الاحتياجات بما تجيب عنه المقاطع وما تستبعده صراحة.</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="63" t="inlineStr">
-        <is>
-          <t>الحاجة</t>
-        </is>
-      </c>
-      <c r="B4" s="63" t="inlineStr">
-        <is>
-          <t>عدد المقاطع</t>
-        </is>
-      </c>
-      <c r="C4" s="63" t="inlineStr">
-        <is>
-          <t>تعريف</t>
-        </is>
-      </c>
-      <c r="D4" s="63" t="inlineStr">
-        <is>
-          <t>شرح</t>
-        </is>
-      </c>
-      <c r="E4" s="63" t="inlineStr">
-        <is>
-          <t>تعليم</t>
-        </is>
-      </c>
-      <c r="F4" s="63" t="inlineStr">
-        <is>
-          <t>استدلال</t>
-        </is>
-      </c>
-      <c r="G4" s="63" t="inlineStr">
-        <is>
-          <t>معالجة اعتراض</t>
-        </is>
-      </c>
-      <c r="H4" s="63" t="inlineStr">
-        <is>
-          <t>مقارنة</t>
-        </is>
-      </c>
-      <c r="I4" s="63" t="inlineStr">
-        <is>
-          <t>بحث أو تحقيق</t>
-        </is>
-      </c>
-      <c r="J4" s="63" t="inlineStr">
-        <is>
-          <t>توجيه عملي</t>
-        </is>
-      </c>
-      <c r="K4" s="63" t="inlineStr">
-        <is>
-          <t>الحكم</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="67" t="inlineStr">
-        <is>
-          <t>ح1</t>
-        </is>
-      </c>
-      <c r="B5" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="C5" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="67" t="inlineStr">
-        <is>
-          <t>جيد؛ بقيت فجوتان: مقارنة مباشرة بين القرآن والحديث النبوي، والمقارنة العامة بين دور القرآن والإنجيل.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="67" t="inlineStr">
-        <is>
-          <t>ح5</t>
-        </is>
-      </c>
-      <c r="B6" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="67" t="inlineStr">
-        <is>
-          <t>جيد في عرض الموضوعات والقصص؛ لا يغطي استدلالاً مستقلاً على تاريخية القصص.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="67" t="inlineStr">
-        <is>
-          <t>ح2</t>
-        </is>
-      </c>
-      <c r="B7" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="67" t="inlineStr">
-        <is>
-          <t>جيد؛ بقيت فجوات في تعريف الوحي المباشر، ومدة النزول، وأول ما نزل.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="67" t="inlineStr">
-        <is>
-          <t>ح3</t>
-        </is>
-      </c>
-      <c r="B8" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="67" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="67" t="inlineStr">
-        <is>
-          <t>جيد؛ المقارنة المباشرة بين جمع أبي بكر وجمع عثمان تغطيتها جزئية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="67" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="B9" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="67" t="inlineStr">
-        <is>
-          <t>غير مكتمل عملياً؛ تعريف البنية موجود لكن الوصول إلى آية/جزء محدد غير مغطى.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="67" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="B10" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="67" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="67" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" s="67" t="inlineStr">
-        <is>
-          <t>غير مكتمل عملياً؛ توجد مواد للفهم والفضل والترجمة، لكن نقطة البداية واختيار تفسير للمبتدئ غير مغطاتين.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>ح7</t>
-        </is>
-      </c>
-      <c r="B11" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="67" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="67" t="inlineStr">
-        <is>
-          <t>جيد في الاستدلال والاعتراضات؛ بقيت فجوة فرعية في سؤال معرفة النبي ﷺ بالقراءة والكتابة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t>فجوات واضحة تحتاج محتوى أو معالجة صريحة</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="n"/>
-      <c r="C15" s="1" t="n"/>
-      <c r="D15" s="1" t="n"/>
-      <c r="E15" s="1" t="n"/>
-      <c r="F15" s="1" t="n"/>
-      <c r="G15" s="1" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="63" t="inlineStr">
-        <is>
-          <t>الحاجة</t>
-        </is>
-      </c>
-      <c r="B16" s="63" t="inlineStr">
-        <is>
-          <t>السؤال/الفجوة</t>
-        </is>
-      </c>
-      <c r="C16" s="63" t="inlineStr">
-        <is>
-          <t>نوع الفجوة</t>
-        </is>
-      </c>
-      <c r="D16" s="63" t="inlineStr">
-        <is>
-          <t>الأولوية</t>
-        </is>
-      </c>
-      <c r="E16" s="63" t="inlineStr">
-        <is>
-          <t>الدليل من السجل</t>
-        </is>
-      </c>
-      <c r="F16" s="63" t="inlineStr">
-        <is>
-          <t>الحالة</t>
-        </is>
-      </c>
-      <c r="G16" s="63" t="inlineStr">
-        <is>
-          <t>الإجراء الهيكلي</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1" s="49">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>ح1</t>
-        </is>
-      </c>
-      <c r="B17" s="67" t="inlineStr">
-        <is>
-          <t>ما الفرق بين القرآن والحديث؟</t>
-        </is>
-      </c>
-      <c r="C17" s="67" t="inlineStr">
-        <is>
-          <t>تغطية مباشرة مفقودة</t>
-        </is>
-      </c>
-      <c r="D17" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E17" s="67" t="inlineStr">
-        <is>
-          <t>ق-35 يستبعد الفرق الشامل بين القرآن والحديث النبوي؛ ق-32 يعالج حجية السنة.</t>
-        </is>
-      </c>
-      <c r="F17" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى مباشرة</t>
-        </is>
-      </c>
-      <c r="G17" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقطع مقارنة مباشر أو إعلان عدم التغطية.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1" s="49">
-      <c r="A18" s="67" t="inlineStr">
-        <is>
-          <t>ح2</t>
-        </is>
-      </c>
-      <c r="B18" s="67" t="inlineStr">
-        <is>
-          <t>كم سنة استمر نزول القرآن؟</t>
-        </is>
-      </c>
-      <c r="C18" s="67" t="inlineStr">
-        <is>
-          <t>معلومة تأسيسية مفقودة</t>
-        </is>
-      </c>
-      <c r="D18" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E18" s="67" t="inlineStr">
-        <is>
-          <t>مذكور ضمن صياغات الحاجة ح2 ولا يوجد مقطع يجيب عنها مباشرة.</t>
-        </is>
-      </c>
-      <c r="F18" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G18" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقتطف موثق مباشر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1" s="49">
-      <c r="A19" s="67" t="inlineStr">
-        <is>
-          <t>ح2</t>
-        </is>
-      </c>
-      <c r="B19" s="67" t="inlineStr">
-        <is>
-          <t>ما أول آية نزلت؟</t>
-        </is>
-      </c>
-      <c r="C19" s="67" t="inlineStr">
-        <is>
-          <t>معلومة تأسيسية مفقودة</t>
-        </is>
-      </c>
-      <c r="D19" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E19" s="67" t="inlineStr">
-        <is>
-          <t>مذكور ضمن صياغات الحاجة ح2 ولا يوجد مقطع يجيب عنها مباشرة.</t>
-        </is>
-      </c>
-      <c r="F19" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G19" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقتطف موثق مباشر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1" s="49">
-      <c r="A20" s="67" t="inlineStr">
-        <is>
-          <t>ح3</t>
-        </is>
-      </c>
-      <c r="B20" s="67" t="inlineStr">
-        <is>
-          <t>ما الفرق بين جمع أبي بكر وجمع عثمان؟</t>
-        </is>
-      </c>
-      <c r="C20" s="67" t="inlineStr">
-        <is>
-          <t>مقارنة جزئية</t>
-        </is>
-      </c>
-      <c r="D20" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E20" s="67" t="inlineStr">
-        <is>
-          <t>ق-13 يذكر صراحة أنه لا يجيب عن المقارنة؛ ق-33 يعرض المراحل دون مقارنة مركزة.</t>
-        </is>
-      </c>
-      <c r="F20" s="67" t="inlineStr">
-        <is>
-          <t>جزئي</t>
-        </is>
-      </c>
-      <c r="G20" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقارنة قصيرة أو PARTIAL بحدود واضحة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1" s="49">
-      <c r="A21" s="67" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="B21" s="67" t="inlineStr">
-        <is>
-          <t>كيف أجد آية في المصحف؟</t>
-        </is>
-      </c>
-      <c r="C21" s="67" t="inlineStr">
-        <is>
-          <t>تعليم عملي مفقود</t>
-        </is>
-      </c>
-      <c r="D21" s="67" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="E21" s="67" t="inlineStr">
-        <is>
-          <t>ق-15 يسجلها ضمن الأسئلة القريبة التي لا يجيب عنها.</t>
-        </is>
-      </c>
-      <c r="F21" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G21" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقطع/إرشاد عملي مستقل.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1" s="49">
-      <c r="A22" s="67" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="B22" s="67" t="inlineStr">
-        <is>
-          <t>ما معنى جزء عمّ؟</t>
-        </is>
-      </c>
-      <c r="C22" s="67" t="inlineStr">
-        <is>
-          <t>تعريف عملي مفقود</t>
-        </is>
-      </c>
-      <c r="D22" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E22" s="67" t="inlineStr">
-        <is>
-          <t>مذكور ضمن صياغات الحاجة ح4 ولا يوجد مقطع مباشر.</t>
-        </is>
-      </c>
-      <c r="F22" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G22" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقتطف تعريفي مباشر.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1" s="49">
-      <c r="A23" s="67" t="inlineStr">
-        <is>
-          <t>ح4</t>
-        </is>
-      </c>
-      <c r="B23" s="67" t="inlineStr">
-        <is>
-          <t>كيف أعرف رقم الآية؟</t>
-        </is>
-      </c>
-      <c r="C23" s="67" t="inlineStr">
-        <is>
-          <t>تعليم عملي مفقود</t>
-        </is>
-      </c>
-      <c r="D23" s="67" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="E23" s="67" t="inlineStr">
-        <is>
-          <t>مذكور ضمن صياغات الحاجة ح4 ولا يوجد مقطع مباشر.</t>
-        </is>
-      </c>
-      <c r="F23" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G23" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقطع/إرشاد عملي مستقل.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1" s="49">
-      <c r="A24" s="67" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="B24" s="67" t="inlineStr">
-        <is>
-          <t>من أين أبدأ قراءة القرآن؟</t>
-        </is>
-      </c>
-      <c r="C24" s="67" t="inlineStr">
-        <is>
-          <t>توجيه عملي مفقود</t>
-        </is>
-      </c>
-      <c r="D24" s="67" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="E24" s="67" t="inlineStr">
-        <is>
-          <t>ق-18 في ورقة «الناقص» الأصلية: من أين يبدأ المبتدئ القراءة.</t>
-        </is>
-      </c>
-      <c r="F24" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G24" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مادة بداية عملية قبل التجميد.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1" s="49">
-      <c r="A25" s="67" t="inlineStr">
-        <is>
-          <t>ح6</t>
-        </is>
-      </c>
-      <c r="B25" s="67" t="inlineStr">
-        <is>
-          <t>ما أفضل تفسير للمبتدئ؟</t>
-        </is>
-      </c>
-      <c r="C25" s="67" t="inlineStr">
-        <is>
-          <t>توجيه مصدر مفقود</t>
-        </is>
-      </c>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>ق-19 يسجل السؤال ضمن الأسئلة القريبة التي لا يجيب عنها.</t>
-        </is>
-      </c>
-      <c r="F25" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G25" s="67" t="inlineStr">
-        <is>
-          <t>إضافة توصية مصدر مراجعة وفق سياسة المرجعية أو إحالة مضبوطة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1" s="49">
-      <c r="A26" s="67" t="inlineStr">
-        <is>
-          <t>ح7</t>
-        </is>
-      </c>
-      <c r="B26" s="67" t="inlineStr">
-        <is>
-          <t>هل كان النبي يعرف القراءة والكتابة؟</t>
-        </is>
-      </c>
-      <c r="C26" s="67" t="inlineStr">
-        <is>
-          <t>استدلال فرعي مفقود</t>
-        </is>
-      </c>
-      <c r="D26" s="67" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E26" s="67" t="inlineStr">
-        <is>
-          <t>مذكور ضمن صياغات الحاجة ح7 ولا يوجد مقطع يجيب عنه مباشرة.</t>
-        </is>
-      </c>
-      <c r="F26" s="67" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G26" s="67" t="inlineStr">
-        <is>
-          <t>إضافة مقتطف موثق إذا سيبقى السؤال ضمن الوعود النشطة.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="42" customHeight="1" s="49">
-      <c r="A27" s="94" t="inlineStr">
-        <is>
-          <t>ح1</t>
-        </is>
-      </c>
-      <c r="B27" s="94" t="inlineStr">
-        <is>
-          <t>هل القرآن مثل الإنجيل عند المسيحيين؟</t>
-        </is>
-      </c>
-      <c r="C27" s="94" t="inlineStr">
-        <is>
-          <t>مقارنة عامة ملتبسة وغير مغطاة مباشرة</t>
-        </is>
-      </c>
-      <c r="D27" s="94" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E27" s="94" t="inlineStr">
-        <is>
-          <t>ق-03 يشرح علاقة القرآن بالكتب السابقة، لا المقارنة بين دور القرآن عند المسلمين ودور الإنجيل عند المسيحيين.</t>
-        </is>
-      </c>
-      <c r="F27" s="94" t="inlineStr">
-        <is>
-          <t>غير مغطى مباشرة</t>
-        </is>
-      </c>
-      <c r="G27" s="94" t="inlineStr">
-        <is>
-          <t>CLARIFY حسب المقصود، أو NOT_COVERED إذا كان المقصود مقارنة الدور الديني العامة.</t>
-        </is>
-      </c>
-      <c r="H27" s="94" t="n"/>
-      <c r="I27" s="94" t="n"/>
-      <c r="J27" s="94" t="n"/>
-      <c r="K27" s="94" t="n"/>
-    </row>
-    <row r="28" ht="42" customHeight="1" s="49">
-      <c r="A28" s="93" t="inlineStr">
-        <is>
-          <t>ح2</t>
-        </is>
-      </c>
-      <c r="B28" s="93" t="inlineStr">
-        <is>
-          <t>ما هو الوحي؟</t>
-        </is>
-      </c>
-      <c r="C28" s="93" t="inlineStr">
-        <is>
-          <t>تعريف تأسيسي غير مباشر</t>
-        </is>
-      </c>
-      <c r="D28" s="93" t="inlineStr">
-        <is>
-          <t>عالية</t>
-        </is>
-      </c>
-      <c r="E28" s="93" t="inlineStr">
-        <is>
-          <t>ق-08 يشرح صور مجيء الوحي للنبي ﷺ، لكنه لا يقدم تعريفاً تمهيدياً مستقلاً لمفهوم الوحي.</t>
-        </is>
-      </c>
-      <c r="F28" s="93" t="inlineStr">
-        <is>
-          <t>جزئي</t>
-        </is>
-      </c>
-      <c r="G28" s="93" t="inlineStr">
-        <is>
-          <t>PARTIAL أو إضافة تعريف مباشر قبل توسيع الوعد.</t>
-        </is>
-      </c>
-      <c r="H28" s="93" t="n"/>
-      <c r="I28" s="93" t="n"/>
-      <c r="J28" s="93" t="n"/>
-      <c r="K28" s="93" t="n"/>
-    </row>
-    <row r="29" ht="42" customHeight="1" s="49">
-      <c r="A29" s="94" t="inlineStr">
-        <is>
-          <t>ح5</t>
-        </is>
-      </c>
-      <c r="B29" s="94" t="inlineStr">
-        <is>
-          <t>كيف نعرف أن قصص القرآن حقيقية؟</t>
-        </is>
-      </c>
-      <c r="C29" s="94" t="inlineStr">
-        <is>
-          <t>استدلال/اعتراض غير مغطى</t>
-        </is>
-      </c>
-      <c r="D29" s="94" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E29" s="94" t="inlineStr">
-        <is>
-          <t>ق-06 يعرّف القصص وأنواعها وغاياتها، لكنه لا يقدم دليلاً مستقلاً لمن يطلب إثبات تاريخيتها.</t>
-        </is>
-      </c>
-      <c r="F29" s="94" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G29" s="94" t="inlineStr">
-        <is>
-          <t>NOT_COVERED ضمن النسخة الحالية ما لم تضاف مادة استدلالية مستقلة.</t>
-        </is>
-      </c>
-      <c r="H29" s="94" t="n"/>
-      <c r="I29" s="94" t="n"/>
-      <c r="J29" s="94" t="n"/>
-      <c r="K29" s="94" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="95" t="inlineStr">
-        <is>
-          <t>ح1</t>
-        </is>
-      </c>
-      <c r="B30" s="95" t="inlineStr">
-        <is>
-          <t>هل القرآن مثل الإنجيل عند المسيحيين؟</t>
-        </is>
-      </c>
-      <c r="C30" s="95" t="inlineStr">
-        <is>
-          <t>مقارنة غير مغطاة</t>
-        </is>
-      </c>
-      <c r="D30" s="95" t="inlineStr">
-        <is>
-          <t>متوسطة</t>
-        </is>
-      </c>
-      <c r="E30" s="95" t="inlineStr">
-        <is>
-          <t>v22: ق-03 يستبعدها صراحة؛ يجيب عن صلة القرآن بالكتب السابقة لا عن مقارنة دوره بدور الإنجيل.</t>
-        </is>
-      </c>
-      <c r="F30" s="95" t="inlineStr">
-        <is>
-          <t>غير مغطى</t>
-        </is>
-      </c>
-      <c r="G30" s="95" t="inlineStr">
-        <is>
-          <t>حُذفت من صياغات ح1 النشطة؛ تُضاف مادة مقارنة مباشرة أو يبقى الامتناع.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A15:G15"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D17:D26">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>D17="عالية"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="49" min="1" max="1"/>
@@ -1075,6 +1075,18 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>v23 (المرشحة النهائية، 5 أكتوبر 2026): v22 + قرارات المنع والاستيضاح الأخيرة (ق-14، ق-25، ق-06)، وقالبا استيضاح مرجعيان غير مفعّلين (ست-07، ست-08)، وفجوات جديدة، و«سجل التغييرات». صفر تغييرات في النص المرجعي. القاعدة: المنع لما لا يصلح للسؤال أصلاً؛ PARTIAL لما يفيد دون أن يكمل؛ CLARIFY لما يحتمل معنى يجيب عنه المقطع ومعنى لا يجيب عنه.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>النسخة v24</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>v24 (5 أكتوبر 2026): v23 + إزالة منع «كم مرة تحديداً نزل القرآن؟» من ق-37 (PARTIAL). صفر تغييرات في النص المرجعي.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1155,6 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -1474,9 +1485,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="45" t="inlineStr">
         <is>
@@ -5385,7 +5393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="49" min="1" max="1"/>
@@ -6362,6 +6370,60 @@
         </is>
       </c>
       <c r="E36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>v24</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ق-37</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>أسئلة قريبة لا يجيب عنها</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>حُذف «كم مرة تحديداً نزل القرآن؟»؛ وأُضيف «لا يحدد عددًا معينًا لمرات نزول القرآن.» إلى «لا يجيب عن»</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PARTIAL بـ ق-37 لا منع (ملف Unified Gold: Library Preconditions)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>v24</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>النص المرجعي</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0 تغييرات</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8894,12 +8956,12 @@
       </c>
       <c r="X18" s="67" t="inlineStr">
         <is>
-          <t>لا يجيب عن شهر النزول أو كيفية مجيء الوحي للنبي.</t>
+          <t>لا يجيب عن شهر النزول أو كيفية مجيء الوحي للنبي. لا يحدد عددًا معينًا لمرات نزول القرآن.</t>
         </is>
       </c>
       <c r="Y18" s="67" t="inlineStr">
         <is>
-          <t>في أي شهر نزل القرآن؟ | كيف كان الوحي يأتي النبي؟ | كم مرة تحديداً نزل القرآن؟</t>
+          <t>في أي شهر نزل القرآن؟ | كيف كان الوحي يأتي النبي؟</t>
         </is>
       </c>
       <c r="Z18" s="67" t="inlineStr">
@@ -12256,8 +12318,8 @@
   <mergeCells count="6">
     <mergeCell ref="A2:AH2"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="AB3:AH3"/>
-    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="A1:AH1"/>
     <mergeCell ref="E3:M3"/>
   </mergeCells>
@@ -12346,7 +12408,6 @@
       <c r="N2" s="1" t="n"/>
       <c r="O2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -13319,7 +13380,6 @@
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>

--- a/data/register.xlsx
+++ b/data/register.xlsx
@@ -867,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" style="49" min="1" max="1"/>
@@ -1087,6 +1087,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>v24 (5 أكتوبر 2026): v23 + إزالة منع «كم مرة تحديداً نزل القرآن؟» من ق-37 (PARTIAL). صفر تغييرات في النص المرجعي.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>النسخة v25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>v25 (5 أكتوبر 2026): v24 + حذف «ما الرسالة الأساسية في القرآن؟» من ق-05 وتسجيله فجوة. صفر تغييرات في النص المرجعي.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="49" min="1" max="1"/>
@@ -1155,6 +1167,7 @@
       <c r="J2" s="1" t="n"/>
       <c r="K2" s="1" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -1485,6 +1498,9 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="45" t="inlineStr">
         <is>
@@ -2173,6 +2189,43 @@
       <c r="G33" s="95" t="inlineStr">
         <is>
           <t>إضافة مادة أو الامتناع.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="95" t="inlineStr">
+        <is>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="B34" s="95" t="inlineStr">
+        <is>
+          <t>ما الرسالة الأساسية في القرآن؟</t>
+        </is>
+      </c>
+      <c r="C34" s="95" t="inlineStr">
+        <is>
+          <t>تحديد مفقود</t>
+        </is>
+      </c>
+      <c r="D34" s="95" t="inlineStr">
+        <is>
+          <t>متوسطة</t>
+        </is>
+      </c>
+      <c r="E34" s="95" t="inlineStr">
+        <is>
+          <t>v25: ق-05 يعدد أبرز الموضوعات ولا يحدد رسالة واحدة؛ حُذفت الصياغة من ق-05 (قياس السجل v24: ق-05/r2).</t>
+        </is>
+      </c>
+      <c r="F34" s="95" t="inlineStr">
+        <is>
+          <t>غير مغطى</t>
+        </is>
+      </c>
+      <c r="G34" s="95" t="inlineStr">
+        <is>
+          <t>إضافة مادة مباشرة أو الامتناع.</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="49" min="1" max="1"/>
@@ -6424,6 +6477,114 @@
         </is>
       </c>
       <c r="E38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>v25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ق-05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>حُذف «ما الرسالة الأساسية في القرآن؟»؛ وأُضيف «يعدد أبرز موضوعات القرآن، ولا يحدد رسالة واحدة بوصفها الرسالة الأساسية للقرآن.» إلى الحدود و«لا يجيب عن»</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>ق-05 لا يحدد رسالة واحدة (قياس السجل v24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>v25</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ح5</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>«ما الرسالة الأساسية في القرآن؟» موسوم [فجوة]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>لا يُصدَّر للموجّه</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>v25</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ق-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>صياغات المستخدم</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>لا تغيير: «لماذا لم ير الناس جبريل؟» موجود أصلاً في صياغاته</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ق-30 يجيب عنه (حكمة خفاء الوحي والابتلاء)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>v25</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>النص المرجعي</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>0 تغييرات</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -7787,7 +7948,7 @@
       </c>
       <c r="O11" s="67" t="inlineStr">
         <is>
-          <t>عن ماذا يتكلم القرآن؟ | ما الرسالة الأساسية في القرآن؟ | هل القرآن كتاب أحكام فقط؟ | هل يتكلم القرآن عن يوم القيامة؟ | ماذا يطلب القرآن من الإنسان؟</t>
+          <t>عن ماذا يتكلم القرآن؟ | هل القرآن كتاب أحكام فقط؟ | هل يتكلم القرآن عن يوم القيامة؟ | ماذا يطلب القرآن من الإنسان؟</t>
         </is>
       </c>
       <c r="P11" s="67" t="inlineStr">
@@ -7827,12 +7988,12 @@
       </c>
       <c r="W11" s="67" t="inlineStr">
         <is>
-          <t>يلخص أبرز موضوعات القرآن، ولا يفسر سورة أو قصة بعينها.</t>
+          <t>يلخص أبرز موضوعات القرآن، ولا يفسر سورة أو قصة بعينها. يعدد أبرز موضوعات القرآن، ولا يحدد رسالة واحدة بوصفها الرسالة الأساسية للقرآن.</t>
         </is>
       </c>
       <c r="X11" s="67" t="inlineStr">
         <is>
-          <t>لا يجيب عن قصة نبي بعينه ولا عن تفسير سورة محددة.</t>
+          <t>لا يجيب عن قصة نبي بعينه ولا عن تفسير سورة محددة. يعدد أبرز موضوعات القرآن، ولا يحدد رسالة واحدة بوصفها الرسالة الأساسية للقرآن.</t>
         </is>
       </c>
       <c r="Y11" s="67" t="inlineStr">
@@ -12317,8 +12478,8 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:AH2"/>
+    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="N3:AA3"/>
     <mergeCell ref="AB3:AH3"/>
     <mergeCell ref="A1:AH1"/>
     <mergeCell ref="E3:M3"/>
@@ -12408,6 +12569,7 @@
       <c r="N2" s="1" t="n"/>
       <c r="O2" s="1" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="63" t="inlineStr">
         <is>
@@ -12588,7 +12750,7 @@
       </c>
       <c r="F6" s="67" t="inlineStr">
         <is>
-          <t>«عن ماذا يتكلم القرآن؟» · «ما الرسالة الأساسية في القرآن؟» · «هل القرآن فيه قصص؟» · «هل القرآن كتاب أحكام فقط؟» · «ماذا يطلب القرآن من الإنسان؟» · «هل يتكلم القرآن عن يوم القيامة؟»</t>
+          <t>«عن ماذا يتكلم القرآن؟» · «ما الرسالة الأساسية في القرآن؟» [فجوة] · «هل القرآن فيه قصص؟» · «هل القرآن كتاب أحكام فقط؟» · «ماذا يطلب القرآن من الإنسان؟» · «هل يتكلم القرآن عن يوم القيامة؟»</t>
         </is>
       </c>
       <c r="G6" s="67" t="inlineStr">
